--- a/docs/modeles/Modele_points_GPS_Taladz.xlsx
+++ b/docs/modeles/Modele_points_GPS_Taladz.xlsx
@@ -1409,7 +1409,7 @@
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Arris / أريس</t>
+          <t>Tkout / تكوت</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">

--- a/docs/modeles/Modele_points_GPS_Taladz.xlsx
+++ b/docs/modeles/Modele_points_GPS_Taladz.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Site" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Points" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Listes" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Types" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Site" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Points" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Listes" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="LISTE_WILAYAS">Listes!$A$2:$A$59</definedName>
@@ -620,7 +621,7 @@
     <definedName name="D_547">Listes!$H$1540:$H$1541</definedName>
     <definedName name="D_548">Listes!$H$1542:$H$1542</definedName>
     <definedName name="W_58">Listes!$F$548:$F$549</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Points'!$A$1:$L$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Points'!$A$1:$L$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -631,7 +632,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -656,9 +657,13 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="005F6B3A"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -669,6 +674,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005F6B3A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
@@ -676,11 +687,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00808080"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -714,12 +720,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="005F6B3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005F6B3A"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -754,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -765,31 +771,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1157,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1221,77 +1235,84 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Le type se choisit dans une liste : la feuille « Types » explique lequel prendre, avec des exemples. En cas de doute, prenez le plus proche et précisez dans « Description » (ex. « mausolée », « gravures rupestres ») : l'équipe Tala DZ corrigera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>La ligne grise « Exemple » montre le format attendu : elle n'est pas importée, vous pouvez la laisser.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>3. Relever un point GPS avec un téléphone</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Google Maps : placez-vous sur le point, faites un appui long sur la carte : les coordonnées s'affichent en haut (ex. 35.484997, 6.467136).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Copiez le premier nombre dans « Latitude » et le second dans « Longitude ». Utilisez le point comme séparateur décimal, pas la virgule.</t>
+          <t>Google Maps : placez-vous sur le point, faites un appui long sur la carte : les coordonnées s'affichent en haut (ex. 35.484997, 6.467136).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Copiez le premier nombre dans « Latitude » et le second dans « Longitude ». Utilisez le point comme séparateur décimal, pas la virgule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Pour l'Algérie, la latitude est entre 18 et 38 et la longitude entre -9 et 12 : le fichier refuse les valeurs hors de ces bornes.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>4. Point à l'intérieur d'un bâtiment (salle d'un musée, pièce d'une maison)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Laissez la latitude et la longitude vides et remplissez « Repère » (ex. 1er étage, salle 3) : le point prendra la position du lieu.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>5. Avant d'envoyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Vérifiez chaque point avec le lien « Voir sur la carte » (dernière colonne). Demandez l'accord des propriétaires pour les lieux privés.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Vérifiez chaque point avec le lien « Voir sur la carte » (dernière colonne). Demandez l'accord des propriétaires pour les lieux privés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Renvoyez le fichier à l'équipe Tala DZ : les points seront ajoutés au lieu et apparaîtront sur sa carte.</t>
         </is>
@@ -1303,6 +1324,241 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Quel type choisir ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Le lieu (feuille « Site ») a un type, et chaque point (feuille « Points ») a le sien : le village de Ghoufi est « Ville / village », son grenier est « Monument », ses gorges « Site naturel ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>En arabe</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Quand le choisir</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Exemples</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Ville / village</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>مدينة / قرية</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Le lieu habité dans son ensemble : village, ville, quartier ancien, ksar entier. Surtout pour la feuille « Site ».</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Ghoufi, la Casbah d’Alger, Taghit, Ksar de Kenadsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Site archéologique</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>موقع أثري</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Les vestiges : ruines antiques, forum, thermes, nécropole, tombeau numide, gravures et peintures rupestres.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Timgad, Djemila, Tipaza, Medracen, Tassili n’Ajjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Monument</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>معلم</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Une construction remarquable encore debout : arc, grenier collectif, fontaine, pont, tour, ancienne maison, statue.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Arc de Trajan, grenier de Taourirt, pont Sidi M’Cid</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Édifice religieux</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>مبنى ديني</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Un lieu de culte ou de mémoire religieuse : mosquée, zaouïa, mausolée de saint, église, chapelle.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Grande Mosquée de Tlemcen, zaouïa, mausolée Sidi Abderrahmane</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Palais / forteresse</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>قصر / حصن</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Un palais ou un ouvrage de défense : palais, casbah, fort, borj, rempart, tour de guet d’un ksar.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Palais du Bey de Constantine, fort de Santa Cruz, borj</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Musée</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>متحف</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Un musée ou une salle d’exposition. Ses salles se relèvent comme points intérieurs (colonne « Repère »).</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Musée de Timgad, salle des mosaïques</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Site naturel</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>موقع طبيعي</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Un lieu de nature : grotte, source, cascade, gorge, palmeraie, belvédère, forêt.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Gorges de Ghoufi, grotte, source thermale, palmeraie</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>أخرى</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Tout le reste : place, marché, atelier d’artisan, lieu de fête ou de mémoire.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Place du village, souk hebdomadaire, atelier de poterie</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1317,173 +1573,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Le lieu principal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Exemple</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Nom du lieu (français)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Ex. Ghoufi</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Nom en arabe</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>غوفي</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Nom en tamazight</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Ɣufi</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Type du lieu</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Ville / village</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Wilaya</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>05 - Batna / باتنة</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Choisir dans la liste</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Daïra</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Tkout / تكوت</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Liste selon la wilaya</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Commune</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Ghassira / غسيرة</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Liste selon la daïra</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Latitude du lieu</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Longitude du lieu</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Rempli par (nom et prénom)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Téléphone ou e-mail</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Date du relevé</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Type du lieu" prompt="Lequel choisir : voir la feuille « Types »" type="list">
       <formula1>"Monument,Site archéologique,Musée,Édifice religieux,Palais / forteresse,Site naturel,Ville / village,Autre"</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Latitude" error="Latitude attendue entre 18 et 38 (Algérie), avec un point décimal" type="decimal" operator="between">
@@ -1508,7 +1764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1532,3912 +1788,3912 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Nom du point</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Nom en arabe</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Nom en tamazight</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Repère (point intérieur)</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Remarque</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Voir sur la carte</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Exemple</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Grenier de Taourirt</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>مخزن تاوريرت</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Taqliɛt n Tewrirt</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Monument</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Grenier collectif en pierre accroché à la falaise.</t>
         </is>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="17" t="n">
         <v>35.123456</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="17" t="n">
         <v>6.123456</v>
       </c>
-      <c r="I2" s="12" t="inlineStr"/>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr"/>
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>Habitant du village</t>
         </is>
       </c>
-      <c r="K2" s="12" t="inlineStr"/>
-      <c r="L2" s="13">
+      <c r="K2" s="17" t="inlineStr"/>
+      <c r="L2" s="18">
         <f>HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G2&amp;","&amp;H2,"Voir sur la carte")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="17" t="n"/>
-      <c r="H3" s="17" t="n"/>
-      <c r="I3" s="16" t="n"/>
-      <c r="J3" s="16" t="n"/>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="18">
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="22">
         <f>IF(AND(ISNUMBER(G3),ISNUMBER(H3)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G3&amp;","&amp;H3,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
-      <c r="I4" s="16" t="n"/>
-      <c r="J4" s="16" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="18">
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="22">
         <f>IF(AND(ISNUMBER(G4),ISNUMBER(H4)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G4&amp;","&amp;H4,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="18">
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="22">
         <f>IF(AND(ISNUMBER(G5),ISNUMBER(H5)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G5&amp;","&amp;H5,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="18">
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="22">
         <f>IF(AND(ISNUMBER(G6),ISNUMBER(H6)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G6&amp;","&amp;H6,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="18">
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="22">
         <f>IF(AND(ISNUMBER(G7),ISNUMBER(H7)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G7&amp;","&amp;H7,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="18">
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="22">
         <f>IF(AND(ISNUMBER(G8),ISNUMBER(H8)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G8&amp;","&amp;H8,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="18">
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="22">
         <f>IF(AND(ISNUMBER(G9),ISNUMBER(H9)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G9&amp;","&amp;H9,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="18">
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="22">
         <f>IF(AND(ISNUMBER(G10),ISNUMBER(H10)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G10&amp;","&amp;H10,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="18">
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="22">
         <f>IF(AND(ISNUMBER(G11),ISNUMBER(H11)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G11&amp;","&amp;H11,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="18">
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="22">
         <f>IF(AND(ISNUMBER(G12),ISNUMBER(H12)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G12&amp;","&amp;H12,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="18">
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="22">
         <f>IF(AND(ISNUMBER(G13),ISNUMBER(H13)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G13&amp;","&amp;H13,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="18">
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="22">
         <f>IF(AND(ISNUMBER(G14),ISNUMBER(H14)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G14&amp;","&amp;H14,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="18">
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="22">
         <f>IF(AND(ISNUMBER(G15),ISNUMBER(H15)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G15&amp;","&amp;H15,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="18">
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="22">
         <f>IF(AND(ISNUMBER(G16),ISNUMBER(H16)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G16&amp;","&amp;H16,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="18">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="22">
         <f>IF(AND(ISNUMBER(G17),ISNUMBER(H17)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G17&amp;","&amp;H17,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="18">
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="22">
         <f>IF(AND(ISNUMBER(G18),ISNUMBER(H18)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G18&amp;","&amp;H18,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="18">
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="22">
         <f>IF(AND(ISNUMBER(G19),ISNUMBER(H19)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G19&amp;","&amp;H19,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="18">
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="22">
         <f>IF(AND(ISNUMBER(G20),ISNUMBER(H20)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G20&amp;","&amp;H20,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="18">
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="22">
         <f>IF(AND(ISNUMBER(G21),ISNUMBER(H21)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G21&amp;","&amp;H21,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="18">
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="22">
         <f>IF(AND(ISNUMBER(G22),ISNUMBER(H22)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G22&amp;","&amp;H22,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="18">
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="22">
         <f>IF(AND(ISNUMBER(G23),ISNUMBER(H23)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G23&amp;","&amp;H23,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="18">
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="22">
         <f>IF(AND(ISNUMBER(G24),ISNUMBER(H24)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G24&amp;","&amp;H24,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="18">
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="22">
         <f>IF(AND(ISNUMBER(G25),ISNUMBER(H25)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G25&amp;","&amp;H25,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="18">
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="22">
         <f>IF(AND(ISNUMBER(G26),ISNUMBER(H26)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G26&amp;","&amp;H26,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="18">
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="22">
         <f>IF(AND(ISNUMBER(G27),ISNUMBER(H27)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G27&amp;","&amp;H27,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="18">
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="22">
         <f>IF(AND(ISNUMBER(G28),ISNUMBER(H28)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G28&amp;","&amp;H28,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="18">
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="22">
         <f>IF(AND(ISNUMBER(G29),ISNUMBER(H29)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G29&amp;","&amp;H29,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="18">
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="22">
         <f>IF(AND(ISNUMBER(G30),ISNUMBER(H30)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G30&amp;","&amp;H30,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="19" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="17" t="n"/>
-      <c r="H31" s="17" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="18">
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="22">
         <f>IF(AND(ISNUMBER(G31),ISNUMBER(H31)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G31&amp;","&amp;H31,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="17" t="n"/>
-      <c r="H32" s="17" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="18">
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="22">
         <f>IF(AND(ISNUMBER(G32),ISNUMBER(H32)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G32&amp;","&amp;H32,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="16" t="n"/>
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="18">
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="22">
         <f>IF(AND(ISNUMBER(G33),ISNUMBER(H33)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G33&amp;","&amp;H33,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="16" t="n"/>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="18">
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="22">
         <f>IF(AND(ISNUMBER(G34),ISNUMBER(H34)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G34&amp;","&amp;H34,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="n"/>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="18">
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="22">
         <f>IF(AND(ISNUMBER(G35),ISNUMBER(H35)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G35&amp;","&amp;H35,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="18">
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="22">
         <f>IF(AND(ISNUMBER(G36),ISNUMBER(H36)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G36&amp;","&amp;H36,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="17" t="n"/>
-      <c r="H37" s="17" t="n"/>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="18">
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="21" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="22">
         <f>IF(AND(ISNUMBER(G37),ISNUMBER(H37)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G37&amp;","&amp;H37,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="18">
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="21" t="n"/>
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="22">
         <f>IF(AND(ISNUMBER(G38),ISNUMBER(H38)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G38&amp;","&amp;H38,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n">
+      <c r="A39" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="17" t="n"/>
-      <c r="H39" s="17" t="n"/>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="18">
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="21" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="22">
         <f>IF(AND(ISNUMBER(G39),ISNUMBER(H39)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G39&amp;","&amp;H39,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="17" t="n"/>
-      <c r="H40" s="17" t="n"/>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="18">
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="22">
         <f>IF(AND(ISNUMBER(G40),ISNUMBER(H40)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G40&amp;","&amp;H40,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n">
+      <c r="A41" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="17" t="n"/>
-      <c r="H41" s="17" t="n"/>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="18">
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="21" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="22">
         <f>IF(AND(ISNUMBER(G41),ISNUMBER(H41)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G41&amp;","&amp;H41,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n">
+      <c r="A42" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="17" t="n"/>
-      <c r="H42" s="17" t="n"/>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="18">
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="21" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="22">
         <f>IF(AND(ISNUMBER(G42),ISNUMBER(H42)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G42&amp;","&amp;H42,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="n">
+      <c r="A43" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="17" t="n"/>
-      <c r="H43" s="17" t="n"/>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="18">
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="21" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="22">
         <f>IF(AND(ISNUMBER(G43),ISNUMBER(H43)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G43&amp;","&amp;H43,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="n">
+      <c r="A44" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="G44" s="17" t="n"/>
-      <c r="H44" s="17" t="n"/>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="18">
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="21" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="22">
         <f>IF(AND(ISNUMBER(G44),ISNUMBER(H44)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G44&amp;","&amp;H44,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="n">
+      <c r="A45" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="15" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="17" t="n"/>
-      <c r="H45" s="17" t="n"/>
-      <c r="I45" s="16" t="n"/>
-      <c r="J45" s="16" t="n"/>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="18">
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="21" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
+      <c r="L45" s="22">
         <f>IF(AND(ISNUMBER(G45),ISNUMBER(H45)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G45&amp;","&amp;H45,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="n">
+      <c r="A46" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="15" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="17" t="n"/>
-      <c r="H46" s="17" t="n"/>
-      <c r="I46" s="16" t="n"/>
-      <c r="J46" s="16" t="n"/>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="18">
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="21" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="22">
         <f>IF(AND(ISNUMBER(G46),ISNUMBER(H46)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G46&amp;","&amp;H46,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="n">
+      <c r="A47" s="19" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="14" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="17" t="n"/>
-      <c r="H47" s="17" t="n"/>
-      <c r="I47" s="16" t="n"/>
-      <c r="J47" s="16" t="n"/>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="18">
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="21" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="22">
         <f>IF(AND(ISNUMBER(G47),ISNUMBER(H47)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G47&amp;","&amp;H47,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="n">
+      <c r="A48" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="15" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="17" t="n"/>
-      <c r="H48" s="17" t="n"/>
-      <c r="I48" s="16" t="n"/>
-      <c r="J48" s="16" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="18">
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="22">
         <f>IF(AND(ISNUMBER(G48),ISNUMBER(H48)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G48&amp;","&amp;H48,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="n">
+      <c r="A49" s="19" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="16" t="n"/>
-      <c r="J49" s="16" t="n"/>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="18">
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="21" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="22">
         <f>IF(AND(ISNUMBER(G49),ISNUMBER(H49)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G49&amp;","&amp;H49,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="15" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="17" t="n"/>
-      <c r="H50" s="17" t="n"/>
-      <c r="I50" s="16" t="n"/>
-      <c r="J50" s="16" t="n"/>
-      <c r="K50" s="16" t="n"/>
-      <c r="L50" s="18">
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="21" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="22">
         <f>IF(AND(ISNUMBER(G50),ISNUMBER(H50)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G50&amp;","&amp;H50,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="n">
+      <c r="A51" s="19" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="17" t="n"/>
-      <c r="H51" s="17" t="n"/>
-      <c r="I51" s="16" t="n"/>
-      <c r="J51" s="16" t="n"/>
-      <c r="K51" s="16" t="n"/>
-      <c r="L51" s="18">
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="22">
         <f>IF(AND(ISNUMBER(G51),ISNUMBER(H51)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G51&amp;","&amp;H51,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="n">
+      <c r="A52" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="15" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="16" t="n"/>
-      <c r="J52" s="16" t="n"/>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="18">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="22">
         <f>IF(AND(ISNUMBER(G52),ISNUMBER(H52)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G52&amp;","&amp;H52,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="n">
+      <c r="A53" s="19" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="16" t="n"/>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="16" t="n"/>
-      <c r="J53" s="16" t="n"/>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="18">
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="21" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="22">
         <f>IF(AND(ISNUMBER(G53),ISNUMBER(H53)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G53&amp;","&amp;H53,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="n">
+      <c r="A54" s="19" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="17" t="n"/>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="16" t="n"/>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="18">
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="22">
         <f>IF(AND(ISNUMBER(G54),ISNUMBER(H54)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G54&amp;","&amp;H54,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="n">
+      <c r="A55" s="19" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="15" t="n"/>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="n"/>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="18">
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="22">
         <f>IF(AND(ISNUMBER(G55),ISNUMBER(H55)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G55&amp;","&amp;H55,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="n">
+      <c r="A56" s="19" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="17" t="n"/>
-      <c r="H56" s="17" t="n"/>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="18">
+      <c r="B56" s="20" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="21" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="22">
         <f>IF(AND(ISNUMBER(G56),ISNUMBER(H56)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G56&amp;","&amp;H56,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="n">
+      <c r="A57" s="19" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="15" t="n"/>
-      <c r="C57" s="16" t="n"/>
-      <c r="D57" s="16" t="n"/>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="17" t="n"/>
-      <c r="H57" s="17" t="n"/>
-      <c r="I57" s="16" t="n"/>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="18">
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="22">
         <f>IF(AND(ISNUMBER(G57),ISNUMBER(H57)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G57&amp;","&amp;H57,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="n">
+      <c r="A58" s="19" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="15" t="n"/>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="16" t="n"/>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="16" t="n"/>
-      <c r="G58" s="17" t="n"/>
-      <c r="H58" s="17" t="n"/>
-      <c r="I58" s="16" t="n"/>
-      <c r="J58" s="16" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="18">
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="21" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="22">
         <f>IF(AND(ISNUMBER(G58),ISNUMBER(H58)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G58&amp;","&amp;H58,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="n">
+      <c r="A59" s="19" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="15" t="n"/>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="16" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="16" t="n"/>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="16" t="n"/>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="18">
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="22">
         <f>IF(AND(ISNUMBER(G59),ISNUMBER(H59)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G59&amp;","&amp;H59,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="n">
+      <c r="A60" s="19" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="16" t="n"/>
-      <c r="D60" s="16" t="n"/>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="16" t="n"/>
-      <c r="G60" s="17" t="n"/>
-      <c r="H60" s="17" t="n"/>
-      <c r="I60" s="16" t="n"/>
-      <c r="J60" s="16" t="n"/>
-      <c r="K60" s="16" t="n"/>
-      <c r="L60" s="18">
+      <c r="B60" s="20" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="22">
         <f>IF(AND(ISNUMBER(G60),ISNUMBER(H60)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G60&amp;","&amp;H60,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="n">
+      <c r="A61" s="19" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="15" t="n"/>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="16" t="n"/>
-      <c r="E61" s="14" t="n"/>
-      <c r="F61" s="16" t="n"/>
-      <c r="G61" s="17" t="n"/>
-      <c r="H61" s="17" t="n"/>
-      <c r="I61" s="16" t="n"/>
-      <c r="J61" s="16" t="n"/>
-      <c r="K61" s="16" t="n"/>
-      <c r="L61" s="18">
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="22">
         <f>IF(AND(ISNUMBER(G61),ISNUMBER(H61)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G61&amp;","&amp;H61,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="n">
+      <c r="A62" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="16" t="n"/>
-      <c r="E62" s="14" t="n"/>
-      <c r="F62" s="16" t="n"/>
-      <c r="G62" s="17" t="n"/>
-      <c r="H62" s="17" t="n"/>
-      <c r="I62" s="16" t="n"/>
-      <c r="J62" s="16" t="n"/>
-      <c r="K62" s="16" t="n"/>
-      <c r="L62" s="18">
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="22">
         <f>IF(AND(ISNUMBER(G62),ISNUMBER(H62)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G62&amp;","&amp;H62,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="n">
+      <c r="A63" s="19" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="15" t="n"/>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="16" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="17" t="n"/>
-      <c r="H63" s="17" t="n"/>
-      <c r="I63" s="16" t="n"/>
-      <c r="J63" s="16" t="n"/>
-      <c r="K63" s="16" t="n"/>
-      <c r="L63" s="18">
+      <c r="B63" s="20" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="22">
         <f>IF(AND(ISNUMBER(G63),ISNUMBER(H63)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G63&amp;","&amp;H63,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="n">
+      <c r="A64" s="19" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="15" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="16" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="16" t="n"/>
-      <c r="G64" s="17" t="n"/>
-      <c r="H64" s="17" t="n"/>
-      <c r="I64" s="16" t="n"/>
-      <c r="J64" s="16" t="n"/>
-      <c r="K64" s="16" t="n"/>
-      <c r="L64" s="18">
+      <c r="B64" s="20" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="21" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="22">
         <f>IF(AND(ISNUMBER(G64),ISNUMBER(H64)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G64&amp;","&amp;H64,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="n">
+      <c r="A65" s="19" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="15" t="n"/>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="16" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="17" t="n"/>
-      <c r="H65" s="17" t="n"/>
-      <c r="I65" s="16" t="n"/>
-      <c r="J65" s="16" t="n"/>
-      <c r="K65" s="16" t="n"/>
-      <c r="L65" s="18">
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="22">
         <f>IF(AND(ISNUMBER(G65),ISNUMBER(H65)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G65&amp;","&amp;H65,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="n">
+      <c r="A66" s="19" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="15" t="n"/>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="16" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="17" t="n"/>
-      <c r="H66" s="17" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="16" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="18">
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="22">
         <f>IF(AND(ISNUMBER(G66),ISNUMBER(H66)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G66&amp;","&amp;H66,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="n">
+      <c r="A67" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="15" t="n"/>
-      <c r="C67" s="16" t="n"/>
-      <c r="D67" s="16" t="n"/>
-      <c r="E67" s="14" t="n"/>
-      <c r="F67" s="16" t="n"/>
-      <c r="G67" s="17" t="n"/>
-      <c r="H67" s="17" t="n"/>
-      <c r="I67" s="16" t="n"/>
-      <c r="J67" s="16" t="n"/>
-      <c r="K67" s="16" t="n"/>
-      <c r="L67" s="18">
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="21" t="n"/>
+      <c r="H67" s="21" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="22">
         <f>IF(AND(ISNUMBER(G67),ISNUMBER(H67)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G67&amp;","&amp;H67,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="14" t="n">
+      <c r="A68" s="19" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="15" t="n"/>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="16" t="n"/>
-      <c r="E68" s="14" t="n"/>
-      <c r="F68" s="16" t="n"/>
-      <c r="G68" s="17" t="n"/>
-      <c r="H68" s="17" t="n"/>
-      <c r="I68" s="16" t="n"/>
-      <c r="J68" s="16" t="n"/>
-      <c r="K68" s="16" t="n"/>
-      <c r="L68" s="18">
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="21" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="22">
         <f>IF(AND(ISNUMBER(G68),ISNUMBER(H68)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G68&amp;","&amp;H68,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14" t="n">
+      <c r="A69" s="19" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="16" t="n"/>
-      <c r="D69" s="16" t="n"/>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="16" t="n"/>
-      <c r="G69" s="17" t="n"/>
-      <c r="H69" s="17" t="n"/>
-      <c r="I69" s="16" t="n"/>
-      <c r="J69" s="16" t="n"/>
-      <c r="K69" s="16" t="n"/>
-      <c r="L69" s="18">
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="22">
         <f>IF(AND(ISNUMBER(G69),ISNUMBER(H69)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G69&amp;","&amp;H69,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14" t="n">
+      <c r="A70" s="19" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="15" t="n"/>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="16" t="n"/>
-      <c r="E70" s="14" t="n"/>
-      <c r="F70" s="16" t="n"/>
-      <c r="G70" s="17" t="n"/>
-      <c r="H70" s="17" t="n"/>
-      <c r="I70" s="16" t="n"/>
-      <c r="J70" s="16" t="n"/>
-      <c r="K70" s="16" t="n"/>
-      <c r="L70" s="18">
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="21" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+      <c r="L70" s="22">
         <f>IF(AND(ISNUMBER(G70),ISNUMBER(H70)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G70&amp;","&amp;H70,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="n">
+      <c r="A71" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="16" t="n"/>
-      <c r="D71" s="16" t="n"/>
-      <c r="E71" s="14" t="n"/>
-      <c r="F71" s="16" t="n"/>
-      <c r="G71" s="17" t="n"/>
-      <c r="H71" s="17" t="n"/>
-      <c r="I71" s="16" t="n"/>
-      <c r="J71" s="16" t="n"/>
-      <c r="K71" s="16" t="n"/>
-      <c r="L71" s="18">
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="22">
         <f>IF(AND(ISNUMBER(G71),ISNUMBER(H71)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G71&amp;","&amp;H71,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14" t="n">
+      <c r="A72" s="19" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="15" t="n"/>
-      <c r="C72" s="16" t="n"/>
-      <c r="D72" s="16" t="n"/>
-      <c r="E72" s="14" t="n"/>
-      <c r="F72" s="16" t="n"/>
-      <c r="G72" s="17" t="n"/>
-      <c r="H72" s="17" t="n"/>
-      <c r="I72" s="16" t="n"/>
-      <c r="J72" s="16" t="n"/>
-      <c r="K72" s="16" t="n"/>
-      <c r="L72" s="18">
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="8" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="22">
         <f>IF(AND(ISNUMBER(G72),ISNUMBER(H72)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G72&amp;","&amp;H72,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="14" t="n">
+      <c r="A73" s="19" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="15" t="n"/>
-      <c r="C73" s="16" t="n"/>
-      <c r="D73" s="16" t="n"/>
-      <c r="E73" s="14" t="n"/>
-      <c r="F73" s="16" t="n"/>
-      <c r="G73" s="17" t="n"/>
-      <c r="H73" s="17" t="n"/>
-      <c r="I73" s="16" t="n"/>
-      <c r="J73" s="16" t="n"/>
-      <c r="K73" s="16" t="n"/>
-      <c r="L73" s="18">
+      <c r="B73" s="20" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="21" t="n"/>
+      <c r="H73" s="21" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="22">
         <f>IF(AND(ISNUMBER(G73),ISNUMBER(H73)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G73&amp;","&amp;H73,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="14" t="n">
+      <c r="A74" s="19" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="15" t="n"/>
-      <c r="C74" s="16" t="n"/>
-      <c r="D74" s="16" t="n"/>
-      <c r="E74" s="14" t="n"/>
-      <c r="F74" s="16" t="n"/>
-      <c r="G74" s="17" t="n"/>
-      <c r="H74" s="17" t="n"/>
-      <c r="I74" s="16" t="n"/>
-      <c r="J74" s="16" t="n"/>
-      <c r="K74" s="16" t="n"/>
-      <c r="L74" s="18">
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="21" t="n"/>
+      <c r="H74" s="21" t="n"/>
+      <c r="I74" s="8" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="22">
         <f>IF(AND(ISNUMBER(G74),ISNUMBER(H74)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G74&amp;","&amp;H74,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="14" t="n">
+      <c r="A75" s="19" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="15" t="n"/>
-      <c r="C75" s="16" t="n"/>
-      <c r="D75" s="16" t="n"/>
-      <c r="E75" s="14" t="n"/>
-      <c r="F75" s="16" t="n"/>
-      <c r="G75" s="17" t="n"/>
-      <c r="H75" s="17" t="n"/>
-      <c r="I75" s="16" t="n"/>
-      <c r="J75" s="16" t="n"/>
-      <c r="K75" s="16" t="n"/>
-      <c r="L75" s="18">
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="21" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="22">
         <f>IF(AND(ISNUMBER(G75),ISNUMBER(H75)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G75&amp;","&amp;H75,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="14" t="n">
+      <c r="A76" s="19" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="15" t="n"/>
-      <c r="C76" s="16" t="n"/>
-      <c r="D76" s="16" t="n"/>
-      <c r="E76" s="14" t="n"/>
-      <c r="F76" s="16" t="n"/>
-      <c r="G76" s="17" t="n"/>
-      <c r="H76" s="17" t="n"/>
-      <c r="I76" s="16" t="n"/>
-      <c r="J76" s="16" t="n"/>
-      <c r="K76" s="16" t="n"/>
-      <c r="L76" s="18">
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="21" t="n"/>
+      <c r="H76" s="21" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="22">
         <f>IF(AND(ISNUMBER(G76),ISNUMBER(H76)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G76&amp;","&amp;H76,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="14" t="n">
+      <c r="A77" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="15" t="n"/>
-      <c r="C77" s="16" t="n"/>
-      <c r="D77" s="16" t="n"/>
-      <c r="E77" s="14" t="n"/>
-      <c r="F77" s="16" t="n"/>
-      <c r="G77" s="17" t="n"/>
-      <c r="H77" s="17" t="n"/>
-      <c r="I77" s="16" t="n"/>
-      <c r="J77" s="16" t="n"/>
-      <c r="K77" s="16" t="n"/>
-      <c r="L77" s="18">
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="21" t="n"/>
+      <c r="H77" s="21" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="22">
         <f>IF(AND(ISNUMBER(G77),ISNUMBER(H77)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G77&amp;","&amp;H77,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="14" t="n">
+      <c r="A78" s="19" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="15" t="n"/>
-      <c r="C78" s="16" t="n"/>
-      <c r="D78" s="16" t="n"/>
-      <c r="E78" s="14" t="n"/>
-      <c r="F78" s="16" t="n"/>
-      <c r="G78" s="17" t="n"/>
-      <c r="H78" s="17" t="n"/>
-      <c r="I78" s="16" t="n"/>
-      <c r="J78" s="16" t="n"/>
-      <c r="K78" s="16" t="n"/>
-      <c r="L78" s="18">
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="19" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="22">
         <f>IF(AND(ISNUMBER(G78),ISNUMBER(H78)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G78&amp;","&amp;H78,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="14" t="n">
+      <c r="A79" s="19" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="15" t="n"/>
-      <c r="C79" s="16" t="n"/>
-      <c r="D79" s="16" t="n"/>
-      <c r="E79" s="14" t="n"/>
-      <c r="F79" s="16" t="n"/>
-      <c r="G79" s="17" t="n"/>
-      <c r="H79" s="17" t="n"/>
-      <c r="I79" s="16" t="n"/>
-      <c r="J79" s="16" t="n"/>
-      <c r="K79" s="16" t="n"/>
-      <c r="L79" s="18">
+      <c r="B79" s="20" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="21" t="n"/>
+      <c r="H79" s="21" t="n"/>
+      <c r="I79" s="8" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
+      <c r="L79" s="22">
         <f>IF(AND(ISNUMBER(G79),ISNUMBER(H79)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G79&amp;","&amp;H79,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="14" t="n">
+      <c r="A80" s="19" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="15" t="n"/>
-      <c r="C80" s="16" t="n"/>
-      <c r="D80" s="16" t="n"/>
-      <c r="E80" s="14" t="n"/>
-      <c r="F80" s="16" t="n"/>
-      <c r="G80" s="17" t="n"/>
-      <c r="H80" s="17" t="n"/>
-      <c r="I80" s="16" t="n"/>
-      <c r="J80" s="16" t="n"/>
-      <c r="K80" s="16" t="n"/>
-      <c r="L80" s="18">
+      <c r="B80" s="20" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="21" t="n"/>
+      <c r="H80" s="21" t="n"/>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="22">
         <f>IF(AND(ISNUMBER(G80),ISNUMBER(H80)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G80&amp;","&amp;H80,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="14" t="n">
+      <c r="A81" s="19" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="15" t="n"/>
-      <c r="C81" s="16" t="n"/>
-      <c r="D81" s="16" t="n"/>
-      <c r="E81" s="14" t="n"/>
-      <c r="F81" s="16" t="n"/>
-      <c r="G81" s="17" t="n"/>
-      <c r="H81" s="17" t="n"/>
-      <c r="I81" s="16" t="n"/>
-      <c r="J81" s="16" t="n"/>
-      <c r="K81" s="16" t="n"/>
-      <c r="L81" s="18">
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="21" t="n"/>
+      <c r="I81" s="8" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="22">
         <f>IF(AND(ISNUMBER(G81),ISNUMBER(H81)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G81&amp;","&amp;H81,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="14" t="n">
+      <c r="A82" s="19" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="15" t="n"/>
-      <c r="C82" s="16" t="n"/>
-      <c r="D82" s="16" t="n"/>
-      <c r="E82" s="14" t="n"/>
-      <c r="F82" s="16" t="n"/>
-      <c r="G82" s="17" t="n"/>
-      <c r="H82" s="17" t="n"/>
-      <c r="I82" s="16" t="n"/>
-      <c r="J82" s="16" t="n"/>
-      <c r="K82" s="16" t="n"/>
-      <c r="L82" s="18">
+      <c r="B82" s="20" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="21" t="n"/>
+      <c r="H82" s="21" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="22">
         <f>IF(AND(ISNUMBER(G82),ISNUMBER(H82)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G82&amp;","&amp;H82,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="14" t="n">
+      <c r="A83" s="19" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="15" t="n"/>
-      <c r="C83" s="16" t="n"/>
-      <c r="D83" s="16" t="n"/>
-      <c r="E83" s="14" t="n"/>
-      <c r="F83" s="16" t="n"/>
-      <c r="G83" s="17" t="n"/>
-      <c r="H83" s="17" t="n"/>
-      <c r="I83" s="16" t="n"/>
-      <c r="J83" s="16" t="n"/>
-      <c r="K83" s="16" t="n"/>
-      <c r="L83" s="18">
+      <c r="B83" s="20" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="19" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="21" t="n"/>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="22">
         <f>IF(AND(ISNUMBER(G83),ISNUMBER(H83)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G83&amp;","&amp;H83,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="14" t="n">
+      <c r="A84" s="19" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="15" t="n"/>
-      <c r="C84" s="16" t="n"/>
-      <c r="D84" s="16" t="n"/>
-      <c r="E84" s="14" t="n"/>
-      <c r="F84" s="16" t="n"/>
-      <c r="G84" s="17" t="n"/>
-      <c r="H84" s="17" t="n"/>
-      <c r="I84" s="16" t="n"/>
-      <c r="J84" s="16" t="n"/>
-      <c r="K84" s="16" t="n"/>
-      <c r="L84" s="18">
+      <c r="B84" s="20" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="19" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="21" t="n"/>
+      <c r="H84" s="21" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="22">
         <f>IF(AND(ISNUMBER(G84),ISNUMBER(H84)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G84&amp;","&amp;H84,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="14" t="n">
+      <c r="A85" s="19" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="15" t="n"/>
-      <c r="C85" s="16" t="n"/>
-      <c r="D85" s="16" t="n"/>
-      <c r="E85" s="14" t="n"/>
-      <c r="F85" s="16" t="n"/>
-      <c r="G85" s="17" t="n"/>
-      <c r="H85" s="17" t="n"/>
-      <c r="I85" s="16" t="n"/>
-      <c r="J85" s="16" t="n"/>
-      <c r="K85" s="16" t="n"/>
-      <c r="L85" s="18">
+      <c r="B85" s="20" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="19" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="21" t="n"/>
+      <c r="H85" s="21" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
+      <c r="L85" s="22">
         <f>IF(AND(ISNUMBER(G85),ISNUMBER(H85)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G85&amp;","&amp;H85,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="14" t="n">
+      <c r="A86" s="19" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="15" t="n"/>
-      <c r="C86" s="16" t="n"/>
-      <c r="D86" s="16" t="n"/>
-      <c r="E86" s="14" t="n"/>
-      <c r="F86" s="16" t="n"/>
-      <c r="G86" s="17" t="n"/>
-      <c r="H86" s="17" t="n"/>
-      <c r="I86" s="16" t="n"/>
-      <c r="J86" s="16" t="n"/>
-      <c r="K86" s="16" t="n"/>
-      <c r="L86" s="18">
+      <c r="B86" s="20" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="21" t="n"/>
+      <c r="H86" s="21" t="n"/>
+      <c r="I86" s="8" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+      <c r="L86" s="22">
         <f>IF(AND(ISNUMBER(G86),ISNUMBER(H86)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G86&amp;","&amp;H86,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="14" t="n">
+      <c r="A87" s="19" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="15" t="n"/>
-      <c r="C87" s="16" t="n"/>
-      <c r="D87" s="16" t="n"/>
-      <c r="E87" s="14" t="n"/>
-      <c r="F87" s="16" t="n"/>
-      <c r="G87" s="17" t="n"/>
-      <c r="H87" s="17" t="n"/>
-      <c r="I87" s="16" t="n"/>
-      <c r="J87" s="16" t="n"/>
-      <c r="K87" s="16" t="n"/>
-      <c r="L87" s="18">
+      <c r="B87" s="20" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="19" t="n"/>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="8" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="22">
         <f>IF(AND(ISNUMBER(G87),ISNUMBER(H87)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G87&amp;","&amp;H87,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="14" t="n">
+      <c r="A88" s="19" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="15" t="n"/>
-      <c r="C88" s="16" t="n"/>
-      <c r="D88" s="16" t="n"/>
-      <c r="E88" s="14" t="n"/>
-      <c r="F88" s="16" t="n"/>
-      <c r="G88" s="17" t="n"/>
-      <c r="H88" s="17" t="n"/>
-      <c r="I88" s="16" t="n"/>
-      <c r="J88" s="16" t="n"/>
-      <c r="K88" s="16" t="n"/>
-      <c r="L88" s="18">
+      <c r="B88" s="20" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="21" t="n"/>
+      <c r="H88" s="21" t="n"/>
+      <c r="I88" s="8" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="22">
         <f>IF(AND(ISNUMBER(G88),ISNUMBER(H88)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G88&amp;","&amp;H88,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="14" t="n">
+      <c r="A89" s="19" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="15" t="n"/>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="16" t="n"/>
-      <c r="E89" s="14" t="n"/>
-      <c r="F89" s="16" t="n"/>
-      <c r="G89" s="17" t="n"/>
-      <c r="H89" s="17" t="n"/>
-      <c r="I89" s="16" t="n"/>
-      <c r="J89" s="16" t="n"/>
-      <c r="K89" s="16" t="n"/>
-      <c r="L89" s="18">
+      <c r="B89" s="20" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="22">
         <f>IF(AND(ISNUMBER(G89),ISNUMBER(H89)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G89&amp;","&amp;H89,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="14" t="n">
+      <c r="A90" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="16" t="n"/>
-      <c r="D90" s="16" t="n"/>
-      <c r="E90" s="14" t="n"/>
-      <c r="F90" s="16" t="n"/>
-      <c r="G90" s="17" t="n"/>
-      <c r="H90" s="17" t="n"/>
-      <c r="I90" s="16" t="n"/>
-      <c r="J90" s="16" t="n"/>
-      <c r="K90" s="16" t="n"/>
-      <c r="L90" s="18">
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="19" t="n"/>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="8" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="22">
         <f>IF(AND(ISNUMBER(G90),ISNUMBER(H90)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G90&amp;","&amp;H90,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="14" t="n">
+      <c r="A91" s="19" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="15" t="n"/>
-      <c r="C91" s="16" t="n"/>
-      <c r="D91" s="16" t="n"/>
-      <c r="E91" s="14" t="n"/>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="17" t="n"/>
-      <c r="H91" s="17" t="n"/>
-      <c r="I91" s="16" t="n"/>
-      <c r="J91" s="16" t="n"/>
-      <c r="K91" s="16" t="n"/>
-      <c r="L91" s="18">
+      <c r="B91" s="20" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="21" t="n"/>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="22">
         <f>IF(AND(ISNUMBER(G91),ISNUMBER(H91)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G91&amp;","&amp;H91,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="14" t="n">
+      <c r="A92" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="15" t="n"/>
-      <c r="C92" s="16" t="n"/>
-      <c r="D92" s="16" t="n"/>
-      <c r="E92" s="14" t="n"/>
-      <c r="F92" s="16" t="n"/>
-      <c r="G92" s="17" t="n"/>
-      <c r="H92" s="17" t="n"/>
-      <c r="I92" s="16" t="n"/>
-      <c r="J92" s="16" t="n"/>
-      <c r="K92" s="16" t="n"/>
-      <c r="L92" s="18">
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="8" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="22">
         <f>IF(AND(ISNUMBER(G92),ISNUMBER(H92)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G92&amp;","&amp;H92,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="14" t="n">
+      <c r="A93" s="19" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="15" t="n"/>
-      <c r="C93" s="16" t="n"/>
-      <c r="D93" s="16" t="n"/>
-      <c r="E93" s="14" t="n"/>
-      <c r="F93" s="16" t="n"/>
-      <c r="G93" s="17" t="n"/>
-      <c r="H93" s="17" t="n"/>
-      <c r="I93" s="16" t="n"/>
-      <c r="J93" s="16" t="n"/>
-      <c r="K93" s="16" t="n"/>
-      <c r="L93" s="18">
+      <c r="B93" s="20" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="19" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="21" t="n"/>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="22">
         <f>IF(AND(ISNUMBER(G93),ISNUMBER(H93)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G93&amp;","&amp;H93,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="14" t="n">
+      <c r="A94" s="19" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="15" t="n"/>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="16" t="n"/>
-      <c r="E94" s="14" t="n"/>
-      <c r="F94" s="16" t="n"/>
-      <c r="G94" s="17" t="n"/>
-      <c r="H94" s="17" t="n"/>
-      <c r="I94" s="16" t="n"/>
-      <c r="J94" s="16" t="n"/>
-      <c r="K94" s="16" t="n"/>
-      <c r="L94" s="18">
+      <c r="B94" s="20" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="19" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="21" t="n"/>
+      <c r="H94" s="21" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="22">
         <f>IF(AND(ISNUMBER(G94),ISNUMBER(H94)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G94&amp;","&amp;H94,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="14" t="n">
+      <c r="A95" s="19" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="15" t="n"/>
-      <c r="C95" s="16" t="n"/>
-      <c r="D95" s="16" t="n"/>
-      <c r="E95" s="14" t="n"/>
-      <c r="F95" s="16" t="n"/>
-      <c r="G95" s="17" t="n"/>
-      <c r="H95" s="17" t="n"/>
-      <c r="I95" s="16" t="n"/>
-      <c r="J95" s="16" t="n"/>
-      <c r="K95" s="16" t="n"/>
-      <c r="L95" s="18">
+      <c r="B95" s="20" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="19" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="8" t="n"/>
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="22">
         <f>IF(AND(ISNUMBER(G95),ISNUMBER(H95)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G95&amp;","&amp;H95,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="14" t="n">
+      <c r="A96" s="19" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="15" t="n"/>
-      <c r="C96" s="16" t="n"/>
-      <c r="D96" s="16" t="n"/>
-      <c r="E96" s="14" t="n"/>
-      <c r="F96" s="16" t="n"/>
-      <c r="G96" s="17" t="n"/>
-      <c r="H96" s="17" t="n"/>
-      <c r="I96" s="16" t="n"/>
-      <c r="J96" s="16" t="n"/>
-      <c r="K96" s="16" t="n"/>
-      <c r="L96" s="18">
+      <c r="B96" s="20" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="19" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="21" t="n"/>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="22">
         <f>IF(AND(ISNUMBER(G96),ISNUMBER(H96)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G96&amp;","&amp;H96,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="14" t="n">
+      <c r="A97" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="15" t="n"/>
-      <c r="C97" s="16" t="n"/>
-      <c r="D97" s="16" t="n"/>
-      <c r="E97" s="14" t="n"/>
-      <c r="F97" s="16" t="n"/>
-      <c r="G97" s="17" t="n"/>
-      <c r="H97" s="17" t="n"/>
-      <c r="I97" s="16" t="n"/>
-      <c r="J97" s="16" t="n"/>
-      <c r="K97" s="16" t="n"/>
-      <c r="L97" s="18">
+      <c r="B97" s="20" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="21" t="n"/>
+      <c r="H97" s="21" t="n"/>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="22">
         <f>IF(AND(ISNUMBER(G97),ISNUMBER(H97)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G97&amp;","&amp;H97,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="14" t="n">
+      <c r="A98" s="19" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="15" t="n"/>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="16" t="n"/>
-      <c r="E98" s="14" t="n"/>
-      <c r="F98" s="16" t="n"/>
-      <c r="G98" s="17" t="n"/>
-      <c r="H98" s="17" t="n"/>
-      <c r="I98" s="16" t="n"/>
-      <c r="J98" s="16" t="n"/>
-      <c r="K98" s="16" t="n"/>
-      <c r="L98" s="18">
+      <c r="B98" s="20" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="19" t="n"/>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="22">
         <f>IF(AND(ISNUMBER(G98),ISNUMBER(H98)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G98&amp;","&amp;H98,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="n">
+      <c r="A99" s="19" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="15" t="n"/>
-      <c r="C99" s="16" t="n"/>
-      <c r="D99" s="16" t="n"/>
-      <c r="E99" s="14" t="n"/>
-      <c r="F99" s="16" t="n"/>
-      <c r="G99" s="17" t="n"/>
-      <c r="H99" s="17" t="n"/>
-      <c r="I99" s="16" t="n"/>
-      <c r="J99" s="16" t="n"/>
-      <c r="K99" s="16" t="n"/>
-      <c r="L99" s="18">
+      <c r="B99" s="20" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="19" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="22">
         <f>IF(AND(ISNUMBER(G99),ISNUMBER(H99)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G99&amp;","&amp;H99,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="14" t="n">
+      <c r="A100" s="19" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="15" t="n"/>
-      <c r="C100" s="16" t="n"/>
-      <c r="D100" s="16" t="n"/>
-      <c r="E100" s="14" t="n"/>
-      <c r="F100" s="16" t="n"/>
-      <c r="G100" s="17" t="n"/>
-      <c r="H100" s="17" t="n"/>
-      <c r="I100" s="16" t="n"/>
-      <c r="J100" s="16" t="n"/>
-      <c r="K100" s="16" t="n"/>
-      <c r="L100" s="18">
+      <c r="B100" s="20" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="19" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="21" t="n"/>
+      <c r="H100" s="21" t="n"/>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="22">
         <f>IF(AND(ISNUMBER(G100),ISNUMBER(H100)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G100&amp;","&amp;H100,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="n">
+      <c r="A101" s="19" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="15" t="n"/>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="16" t="n"/>
-      <c r="E101" s="14" t="n"/>
-      <c r="F101" s="16" t="n"/>
-      <c r="G101" s="17" t="n"/>
-      <c r="H101" s="17" t="n"/>
-      <c r="I101" s="16" t="n"/>
-      <c r="J101" s="16" t="n"/>
-      <c r="K101" s="16" t="n"/>
-      <c r="L101" s="18">
+      <c r="B101" s="20" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="19" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
+      <c r="L101" s="22">
         <f>IF(AND(ISNUMBER(G101),ISNUMBER(H101)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G101&amp;","&amp;H101,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="14" t="n">
+      <c r="A102" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="15" t="n"/>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="16" t="n"/>
-      <c r="E102" s="14" t="n"/>
-      <c r="F102" s="16" t="n"/>
-      <c r="G102" s="17" t="n"/>
-      <c r="H102" s="17" t="n"/>
-      <c r="I102" s="16" t="n"/>
-      <c r="J102" s="16" t="n"/>
-      <c r="K102" s="16" t="n"/>
-      <c r="L102" s="18">
+      <c r="B102" s="20" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="19" t="n"/>
+      <c r="F102" s="8" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="8" t="n"/>
+      <c r="J102" s="8" t="n"/>
+      <c r="K102" s="8" t="n"/>
+      <c r="L102" s="22">
         <f>IF(AND(ISNUMBER(G102),ISNUMBER(H102)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G102&amp;","&amp;H102,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="14" t="n">
+      <c r="A103" s="19" t="n">
         <v>101</v>
       </c>
-      <c r="B103" s="15" t="n"/>
-      <c r="C103" s="16" t="n"/>
-      <c r="D103" s="16" t="n"/>
-      <c r="E103" s="14" t="n"/>
-      <c r="F103" s="16" t="n"/>
-      <c r="G103" s="17" t="n"/>
-      <c r="H103" s="17" t="n"/>
-      <c r="I103" s="16" t="n"/>
-      <c r="J103" s="16" t="n"/>
-      <c r="K103" s="16" t="n"/>
-      <c r="L103" s="18">
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="19" t="n"/>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="21" t="n"/>
+      <c r="H103" s="21" t="n"/>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="22">
         <f>IF(AND(ISNUMBER(G103),ISNUMBER(H103)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G103&amp;","&amp;H103,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="14" t="n">
+      <c r="A104" s="19" t="n">
         <v>102</v>
       </c>
-      <c r="B104" s="15" t="n"/>
-      <c r="C104" s="16" t="n"/>
-      <c r="D104" s="16" t="n"/>
-      <c r="E104" s="14" t="n"/>
-      <c r="F104" s="16" t="n"/>
-      <c r="G104" s="17" t="n"/>
-      <c r="H104" s="17" t="n"/>
-      <c r="I104" s="16" t="n"/>
-      <c r="J104" s="16" t="n"/>
-      <c r="K104" s="16" t="n"/>
-      <c r="L104" s="18">
+      <c r="B104" s="20" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="19" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="8" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+      <c r="L104" s="22">
         <f>IF(AND(ISNUMBER(G104),ISNUMBER(H104)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G104&amp;","&amp;H104,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="14" t="n">
+      <c r="A105" s="19" t="n">
         <v>103</v>
       </c>
-      <c r="B105" s="15" t="n"/>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
-      <c r="E105" s="14" t="n"/>
-      <c r="F105" s="16" t="n"/>
-      <c r="G105" s="17" t="n"/>
-      <c r="H105" s="17" t="n"/>
-      <c r="I105" s="16" t="n"/>
-      <c r="J105" s="16" t="n"/>
-      <c r="K105" s="16" t="n"/>
-      <c r="L105" s="18">
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="19" t="n"/>
+      <c r="F105" s="8" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+      <c r="L105" s="22">
         <f>IF(AND(ISNUMBER(G105),ISNUMBER(H105)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G105&amp;","&amp;H105,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="14" t="n">
+      <c r="A106" s="19" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="15" t="n"/>
-      <c r="C106" s="16" t="n"/>
-      <c r="D106" s="16" t="n"/>
-      <c r="E106" s="14" t="n"/>
-      <c r="F106" s="16" t="n"/>
-      <c r="G106" s="17" t="n"/>
-      <c r="H106" s="17" t="n"/>
-      <c r="I106" s="16" t="n"/>
-      <c r="J106" s="16" t="n"/>
-      <c r="K106" s="16" t="n"/>
-      <c r="L106" s="18">
+      <c r="B106" s="20" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="19" t="n"/>
+      <c r="F106" s="8" t="n"/>
+      <c r="G106" s="21" t="n"/>
+      <c r="H106" s="21" t="n"/>
+      <c r="I106" s="8" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+      <c r="L106" s="22">
         <f>IF(AND(ISNUMBER(G106),ISNUMBER(H106)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G106&amp;","&amp;H106,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="14" t="n">
+      <c r="A107" s="19" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="15" t="n"/>
-      <c r="C107" s="16" t="n"/>
-      <c r="D107" s="16" t="n"/>
-      <c r="E107" s="14" t="n"/>
-      <c r="F107" s="16" t="n"/>
-      <c r="G107" s="17" t="n"/>
-      <c r="H107" s="17" t="n"/>
-      <c r="I107" s="16" t="n"/>
-      <c r="J107" s="16" t="n"/>
-      <c r="K107" s="16" t="n"/>
-      <c r="L107" s="18">
+      <c r="B107" s="20" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="19" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="21" t="n"/>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
+      <c r="L107" s="22">
         <f>IF(AND(ISNUMBER(G107),ISNUMBER(H107)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G107&amp;","&amp;H107,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="14" t="n">
+      <c r="A108" s="19" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="15" t="n"/>
-      <c r="C108" s="16" t="n"/>
-      <c r="D108" s="16" t="n"/>
-      <c r="E108" s="14" t="n"/>
-      <c r="F108" s="16" t="n"/>
-      <c r="G108" s="17" t="n"/>
-      <c r="H108" s="17" t="n"/>
-      <c r="I108" s="16" t="n"/>
-      <c r="J108" s="16" t="n"/>
-      <c r="K108" s="16" t="n"/>
-      <c r="L108" s="18">
+      <c r="B108" s="20" t="n"/>
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="19" t="n"/>
+      <c r="F108" s="8" t="n"/>
+      <c r="G108" s="21" t="n"/>
+      <c r="H108" s="21" t="n"/>
+      <c r="I108" s="8" t="n"/>
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
+      <c r="L108" s="22">
         <f>IF(AND(ISNUMBER(G108),ISNUMBER(H108)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G108&amp;","&amp;H108,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="14" t="n">
+      <c r="A109" s="19" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="15" t="n"/>
-      <c r="C109" s="16" t="n"/>
-      <c r="D109" s="16" t="n"/>
-      <c r="E109" s="14" t="n"/>
-      <c r="F109" s="16" t="n"/>
-      <c r="G109" s="17" t="n"/>
-      <c r="H109" s="17" t="n"/>
-      <c r="I109" s="16" t="n"/>
-      <c r="J109" s="16" t="n"/>
-      <c r="K109" s="16" t="n"/>
-      <c r="L109" s="18">
+      <c r="B109" s="20" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="19" t="n"/>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="8" t="n"/>
+      <c r="J109" s="8" t="n"/>
+      <c r="K109" s="8" t="n"/>
+      <c r="L109" s="22">
         <f>IF(AND(ISNUMBER(G109),ISNUMBER(H109)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G109&amp;","&amp;H109,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="14" t="n">
+      <c r="A110" s="19" t="n">
         <v>108</v>
       </c>
-      <c r="B110" s="15" t="n"/>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="16" t="n"/>
-      <c r="E110" s="14" t="n"/>
-      <c r="F110" s="16" t="n"/>
-      <c r="G110" s="17" t="n"/>
-      <c r="H110" s="17" t="n"/>
-      <c r="I110" s="16" t="n"/>
-      <c r="J110" s="16" t="n"/>
-      <c r="K110" s="16" t="n"/>
-      <c r="L110" s="18">
+      <c r="B110" s="20" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="19" t="n"/>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="21" t="n"/>
+      <c r="H110" s="21" t="n"/>
+      <c r="I110" s="8" t="n"/>
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
+      <c r="L110" s="22">
         <f>IF(AND(ISNUMBER(G110),ISNUMBER(H110)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G110&amp;","&amp;H110,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="14" t="n">
+      <c r="A111" s="19" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="15" t="n"/>
-      <c r="C111" s="16" t="n"/>
-      <c r="D111" s="16" t="n"/>
-      <c r="E111" s="14" t="n"/>
-      <c r="F111" s="16" t="n"/>
-      <c r="G111" s="17" t="n"/>
-      <c r="H111" s="17" t="n"/>
-      <c r="I111" s="16" t="n"/>
-      <c r="J111" s="16" t="n"/>
-      <c r="K111" s="16" t="n"/>
-      <c r="L111" s="18">
+      <c r="B111" s="20" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="19" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="21" t="n"/>
+      <c r="H111" s="21" t="n"/>
+      <c r="I111" s="8" t="n"/>
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="22">
         <f>IF(AND(ISNUMBER(G111),ISNUMBER(H111)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G111&amp;","&amp;H111,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="14" t="n">
+      <c r="A112" s="19" t="n">
         <v>110</v>
       </c>
-      <c r="B112" s="15" t="n"/>
-      <c r="C112" s="16" t="n"/>
-      <c r="D112" s="16" t="n"/>
-      <c r="E112" s="14" t="n"/>
-      <c r="F112" s="16" t="n"/>
-      <c r="G112" s="17" t="n"/>
-      <c r="H112" s="17" t="n"/>
-      <c r="I112" s="16" t="n"/>
-      <c r="J112" s="16" t="n"/>
-      <c r="K112" s="16" t="n"/>
-      <c r="L112" s="18">
+      <c r="B112" s="20" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="19" t="n"/>
+      <c r="F112" s="8" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="8" t="n"/>
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
+      <c r="L112" s="22">
         <f>IF(AND(ISNUMBER(G112),ISNUMBER(H112)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G112&amp;","&amp;H112,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="14" t="n">
+      <c r="A113" s="19" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="15" t="n"/>
-      <c r="C113" s="16" t="n"/>
-      <c r="D113" s="16" t="n"/>
-      <c r="E113" s="14" t="n"/>
-      <c r="F113" s="16" t="n"/>
-      <c r="G113" s="17" t="n"/>
-      <c r="H113" s="17" t="n"/>
-      <c r="I113" s="16" t="n"/>
-      <c r="J113" s="16" t="n"/>
-      <c r="K113" s="16" t="n"/>
-      <c r="L113" s="18">
+      <c r="B113" s="20" t="n"/>
+      <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="19" t="n"/>
+      <c r="F113" s="8" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
+      <c r="L113" s="22">
         <f>IF(AND(ISNUMBER(G113),ISNUMBER(H113)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G113&amp;","&amp;H113,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="14" t="n">
+      <c r="A114" s="19" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="15" t="n"/>
-      <c r="C114" s="16" t="n"/>
-      <c r="D114" s="16" t="n"/>
-      <c r="E114" s="14" t="n"/>
-      <c r="F114" s="16" t="n"/>
-      <c r="G114" s="17" t="n"/>
-      <c r="H114" s="17" t="n"/>
-      <c r="I114" s="16" t="n"/>
-      <c r="J114" s="16" t="n"/>
-      <c r="K114" s="16" t="n"/>
-      <c r="L114" s="18">
+      <c r="B114" s="20" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="19" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="21" t="n"/>
+      <c r="H114" s="21" t="n"/>
+      <c r="I114" s="8" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+      <c r="L114" s="22">
         <f>IF(AND(ISNUMBER(G114),ISNUMBER(H114)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G114&amp;","&amp;H114,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="14" t="n">
+      <c r="A115" s="19" t="n">
         <v>113</v>
       </c>
-      <c r="B115" s="15" t="n"/>
-      <c r="C115" s="16" t="n"/>
-      <c r="D115" s="16" t="n"/>
-      <c r="E115" s="14" t="n"/>
-      <c r="F115" s="16" t="n"/>
-      <c r="G115" s="17" t="n"/>
-      <c r="H115" s="17" t="n"/>
-      <c r="I115" s="16" t="n"/>
-      <c r="J115" s="16" t="n"/>
-      <c r="K115" s="16" t="n"/>
-      <c r="L115" s="18">
+      <c r="B115" s="20" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="19" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="21" t="n"/>
+      <c r="H115" s="21" t="n"/>
+      <c r="I115" s="8" t="n"/>
+      <c r="J115" s="8" t="n"/>
+      <c r="K115" s="8" t="n"/>
+      <c r="L115" s="22">
         <f>IF(AND(ISNUMBER(G115),ISNUMBER(H115)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G115&amp;","&amp;H115,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="14" t="n">
+      <c r="A116" s="19" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="15" t="n"/>
-      <c r="C116" s="16" t="n"/>
-      <c r="D116" s="16" t="n"/>
-      <c r="E116" s="14" t="n"/>
-      <c r="F116" s="16" t="n"/>
-      <c r="G116" s="17" t="n"/>
-      <c r="H116" s="17" t="n"/>
-      <c r="I116" s="16" t="n"/>
-      <c r="J116" s="16" t="n"/>
-      <c r="K116" s="16" t="n"/>
-      <c r="L116" s="18">
+      <c r="B116" s="20" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="19" t="n"/>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="8" t="n"/>
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
+      <c r="L116" s="22">
         <f>IF(AND(ISNUMBER(G116),ISNUMBER(H116)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G116&amp;","&amp;H116,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="14" t="n">
+      <c r="A117" s="19" t="n">
         <v>115</v>
       </c>
-      <c r="B117" s="15" t="n"/>
-      <c r="C117" s="16" t="n"/>
-      <c r="D117" s="16" t="n"/>
-      <c r="E117" s="14" t="n"/>
-      <c r="F117" s="16" t="n"/>
-      <c r="G117" s="17" t="n"/>
-      <c r="H117" s="17" t="n"/>
-      <c r="I117" s="16" t="n"/>
-      <c r="J117" s="16" t="n"/>
-      <c r="K117" s="16" t="n"/>
-      <c r="L117" s="18">
+      <c r="B117" s="20" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="19" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="8" t="n"/>
+      <c r="J117" s="8" t="n"/>
+      <c r="K117" s="8" t="n"/>
+      <c r="L117" s="22">
         <f>IF(AND(ISNUMBER(G117),ISNUMBER(H117)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G117&amp;","&amp;H117,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="14" t="n">
+      <c r="A118" s="19" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="15" t="n"/>
-      <c r="C118" s="16" t="n"/>
-      <c r="D118" s="16" t="n"/>
-      <c r="E118" s="14" t="n"/>
-      <c r="F118" s="16" t="n"/>
-      <c r="G118" s="17" t="n"/>
-      <c r="H118" s="17" t="n"/>
-      <c r="I118" s="16" t="n"/>
-      <c r="J118" s="16" t="n"/>
-      <c r="K118" s="16" t="n"/>
-      <c r="L118" s="18">
+      <c r="B118" s="20" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="19" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="21" t="n"/>
+      <c r="H118" s="21" t="n"/>
+      <c r="I118" s="8" t="n"/>
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
+      <c r="L118" s="22">
         <f>IF(AND(ISNUMBER(G118),ISNUMBER(H118)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G118&amp;","&amp;H118,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="14" t="n">
+      <c r="A119" s="19" t="n">
         <v>117</v>
       </c>
-      <c r="B119" s="15" t="n"/>
-      <c r="C119" s="16" t="n"/>
-      <c r="D119" s="16" t="n"/>
-      <c r="E119" s="14" t="n"/>
-      <c r="F119" s="16" t="n"/>
-      <c r="G119" s="17" t="n"/>
-      <c r="H119" s="17" t="n"/>
-      <c r="I119" s="16" t="n"/>
-      <c r="J119" s="16" t="n"/>
-      <c r="K119" s="16" t="n"/>
-      <c r="L119" s="18">
+      <c r="B119" s="20" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="19" t="n"/>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="21" t="n"/>
+      <c r="H119" s="21" t="n"/>
+      <c r="I119" s="8" t="n"/>
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
+      <c r="L119" s="22">
         <f>IF(AND(ISNUMBER(G119),ISNUMBER(H119)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G119&amp;","&amp;H119,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="14" t="n">
+      <c r="A120" s="19" t="n">
         <v>118</v>
       </c>
-      <c r="B120" s="15" t="n"/>
-      <c r="C120" s="16" t="n"/>
-      <c r="D120" s="16" t="n"/>
-      <c r="E120" s="14" t="n"/>
-      <c r="F120" s="16" t="n"/>
-      <c r="G120" s="17" t="n"/>
-      <c r="H120" s="17" t="n"/>
-      <c r="I120" s="16" t="n"/>
-      <c r="J120" s="16" t="n"/>
-      <c r="K120" s="16" t="n"/>
-      <c r="L120" s="18">
+      <c r="B120" s="20" t="n"/>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="19" t="n"/>
+      <c r="F120" s="8" t="n"/>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
+      <c r="L120" s="22">
         <f>IF(AND(ISNUMBER(G120),ISNUMBER(H120)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G120&amp;","&amp;H120,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="14" t="n">
+      <c r="A121" s="19" t="n">
         <v>119</v>
       </c>
-      <c r="B121" s="15" t="n"/>
-      <c r="C121" s="16" t="n"/>
-      <c r="D121" s="16" t="n"/>
-      <c r="E121" s="14" t="n"/>
-      <c r="F121" s="16" t="n"/>
-      <c r="G121" s="17" t="n"/>
-      <c r="H121" s="17" t="n"/>
-      <c r="I121" s="16" t="n"/>
-      <c r="J121" s="16" t="n"/>
-      <c r="K121" s="16" t="n"/>
-      <c r="L121" s="18">
+      <c r="B121" s="20" t="n"/>
+      <c r="C121" s="8" t="n"/>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="19" t="n"/>
+      <c r="F121" s="8" t="n"/>
+      <c r="G121" s="21" t="n"/>
+      <c r="H121" s="21" t="n"/>
+      <c r="I121" s="8" t="n"/>
+      <c r="J121" s="8" t="n"/>
+      <c r="K121" s="8" t="n"/>
+      <c r="L121" s="22">
         <f>IF(AND(ISNUMBER(G121),ISNUMBER(H121)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G121&amp;","&amp;H121,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="14" t="n">
+      <c r="A122" s="19" t="n">
         <v>120</v>
       </c>
-      <c r="B122" s="15" t="n"/>
-      <c r="C122" s="16" t="n"/>
-      <c r="D122" s="16" t="n"/>
-      <c r="E122" s="14" t="n"/>
-      <c r="F122" s="16" t="n"/>
-      <c r="G122" s="17" t="n"/>
-      <c r="H122" s="17" t="n"/>
-      <c r="I122" s="16" t="n"/>
-      <c r="J122" s="16" t="n"/>
-      <c r="K122" s="16" t="n"/>
-      <c r="L122" s="18">
+      <c r="B122" s="20" t="n"/>
+      <c r="C122" s="8" t="n"/>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="19" t="n"/>
+      <c r="F122" s="8" t="n"/>
+      <c r="G122" s="21" t="n"/>
+      <c r="H122" s="21" t="n"/>
+      <c r="I122" s="8" t="n"/>
+      <c r="J122" s="8" t="n"/>
+      <c r="K122" s="8" t="n"/>
+      <c r="L122" s="22">
         <f>IF(AND(ISNUMBER(G122),ISNUMBER(H122)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G122&amp;","&amp;H122,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="14" t="n">
+      <c r="A123" s="19" t="n">
         <v>121</v>
       </c>
-      <c r="B123" s="15" t="n"/>
-      <c r="C123" s="16" t="n"/>
-      <c r="D123" s="16" t="n"/>
-      <c r="E123" s="14" t="n"/>
-      <c r="F123" s="16" t="n"/>
-      <c r="G123" s="17" t="n"/>
-      <c r="H123" s="17" t="n"/>
-      <c r="I123" s="16" t="n"/>
-      <c r="J123" s="16" t="n"/>
-      <c r="K123" s="16" t="n"/>
-      <c r="L123" s="18">
+      <c r="B123" s="20" t="n"/>
+      <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="19" t="n"/>
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="8" t="n"/>
+      <c r="J123" s="8" t="n"/>
+      <c r="K123" s="8" t="n"/>
+      <c r="L123" s="22">
         <f>IF(AND(ISNUMBER(G123),ISNUMBER(H123)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G123&amp;","&amp;H123,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="14" t="n">
+      <c r="A124" s="19" t="n">
         <v>122</v>
       </c>
-      <c r="B124" s="15" t="n"/>
-      <c r="C124" s="16" t="n"/>
-      <c r="D124" s="16" t="n"/>
-      <c r="E124" s="14" t="n"/>
-      <c r="F124" s="16" t="n"/>
-      <c r="G124" s="17" t="n"/>
-      <c r="H124" s="17" t="n"/>
-      <c r="I124" s="16" t="n"/>
-      <c r="J124" s="16" t="n"/>
-      <c r="K124" s="16" t="n"/>
-      <c r="L124" s="18">
+      <c r="B124" s="20" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="19" t="n"/>
+      <c r="F124" s="8" t="n"/>
+      <c r="G124" s="21" t="n"/>
+      <c r="H124" s="21" t="n"/>
+      <c r="I124" s="8" t="n"/>
+      <c r="J124" s="8" t="n"/>
+      <c r="K124" s="8" t="n"/>
+      <c r="L124" s="22">
         <f>IF(AND(ISNUMBER(G124),ISNUMBER(H124)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G124&amp;","&amp;H124,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="14" t="n">
+      <c r="A125" s="19" t="n">
         <v>123</v>
       </c>
-      <c r="B125" s="15" t="n"/>
-      <c r="C125" s="16" t="n"/>
-      <c r="D125" s="16" t="n"/>
-      <c r="E125" s="14" t="n"/>
-      <c r="F125" s="16" t="n"/>
-      <c r="G125" s="17" t="n"/>
-      <c r="H125" s="17" t="n"/>
-      <c r="I125" s="16" t="n"/>
-      <c r="J125" s="16" t="n"/>
-      <c r="K125" s="16" t="n"/>
-      <c r="L125" s="18">
+      <c r="B125" s="20" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="19" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="21" t="n"/>
+      <c r="H125" s="21" t="n"/>
+      <c r="I125" s="8" t="n"/>
+      <c r="J125" s="8" t="n"/>
+      <c r="K125" s="8" t="n"/>
+      <c r="L125" s="22">
         <f>IF(AND(ISNUMBER(G125),ISNUMBER(H125)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G125&amp;","&amp;H125,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="14" t="n">
+      <c r="A126" s="19" t="n">
         <v>124</v>
       </c>
-      <c r="B126" s="15" t="n"/>
-      <c r="C126" s="16" t="n"/>
-      <c r="D126" s="16" t="n"/>
-      <c r="E126" s="14" t="n"/>
-      <c r="F126" s="16" t="n"/>
-      <c r="G126" s="17" t="n"/>
-      <c r="H126" s="17" t="n"/>
-      <c r="I126" s="16" t="n"/>
-      <c r="J126" s="16" t="n"/>
-      <c r="K126" s="16" t="n"/>
-      <c r="L126" s="18">
+      <c r="B126" s="20" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="19" t="n"/>
+      <c r="F126" s="8" t="n"/>
+      <c r="G126" s="21" t="n"/>
+      <c r="H126" s="21" t="n"/>
+      <c r="I126" s="8" t="n"/>
+      <c r="J126" s="8" t="n"/>
+      <c r="K126" s="8" t="n"/>
+      <c r="L126" s="22">
         <f>IF(AND(ISNUMBER(G126),ISNUMBER(H126)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G126&amp;","&amp;H126,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="14" t="n">
+      <c r="A127" s="19" t="n">
         <v>125</v>
       </c>
-      <c r="B127" s="15" t="n"/>
-      <c r="C127" s="16" t="n"/>
-      <c r="D127" s="16" t="n"/>
-      <c r="E127" s="14" t="n"/>
-      <c r="F127" s="16" t="n"/>
-      <c r="G127" s="17" t="n"/>
-      <c r="H127" s="17" t="n"/>
-      <c r="I127" s="16" t="n"/>
-      <c r="J127" s="16" t="n"/>
-      <c r="K127" s="16" t="n"/>
-      <c r="L127" s="18">
+      <c r="B127" s="20" t="n"/>
+      <c r="C127" s="8" t="n"/>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="19" t="n"/>
+      <c r="F127" s="8" t="n"/>
+      <c r="G127" s="21" t="n"/>
+      <c r="H127" s="21" t="n"/>
+      <c r="I127" s="8" t="n"/>
+      <c r="J127" s="8" t="n"/>
+      <c r="K127" s="8" t="n"/>
+      <c r="L127" s="22">
         <f>IF(AND(ISNUMBER(G127),ISNUMBER(H127)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G127&amp;","&amp;H127,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="14" t="n">
+      <c r="A128" s="19" t="n">
         <v>126</v>
       </c>
-      <c r="B128" s="15" t="n"/>
-      <c r="C128" s="16" t="n"/>
-      <c r="D128" s="16" t="n"/>
-      <c r="E128" s="14" t="n"/>
-      <c r="F128" s="16" t="n"/>
-      <c r="G128" s="17" t="n"/>
-      <c r="H128" s="17" t="n"/>
-      <c r="I128" s="16" t="n"/>
-      <c r="J128" s="16" t="n"/>
-      <c r="K128" s="16" t="n"/>
-      <c r="L128" s="18">
+      <c r="B128" s="20" t="n"/>
+      <c r="C128" s="8" t="n"/>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="19" t="n"/>
+      <c r="F128" s="8" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="8" t="n"/>
+      <c r="J128" s="8" t="n"/>
+      <c r="K128" s="8" t="n"/>
+      <c r="L128" s="22">
         <f>IF(AND(ISNUMBER(G128),ISNUMBER(H128)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G128&amp;","&amp;H128,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="14" t="n">
+      <c r="A129" s="19" t="n">
         <v>127</v>
       </c>
-      <c r="B129" s="15" t="n"/>
-      <c r="C129" s="16" t="n"/>
-      <c r="D129" s="16" t="n"/>
-      <c r="E129" s="14" t="n"/>
-      <c r="F129" s="16" t="n"/>
-      <c r="G129" s="17" t="n"/>
-      <c r="H129" s="17" t="n"/>
-      <c r="I129" s="16" t="n"/>
-      <c r="J129" s="16" t="n"/>
-      <c r="K129" s="16" t="n"/>
-      <c r="L129" s="18">
+      <c r="B129" s="20" t="n"/>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="19" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="21" t="n"/>
+      <c r="H129" s="21" t="n"/>
+      <c r="I129" s="8" t="n"/>
+      <c r="J129" s="8" t="n"/>
+      <c r="K129" s="8" t="n"/>
+      <c r="L129" s="22">
         <f>IF(AND(ISNUMBER(G129),ISNUMBER(H129)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G129&amp;","&amp;H129,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="14" t="n">
+      <c r="A130" s="19" t="n">
         <v>128</v>
       </c>
-      <c r="B130" s="15" t="n"/>
-      <c r="C130" s="16" t="n"/>
-      <c r="D130" s="16" t="n"/>
-      <c r="E130" s="14" t="n"/>
-      <c r="F130" s="16" t="n"/>
-      <c r="G130" s="17" t="n"/>
-      <c r="H130" s="17" t="n"/>
-      <c r="I130" s="16" t="n"/>
-      <c r="J130" s="16" t="n"/>
-      <c r="K130" s="16" t="n"/>
-      <c r="L130" s="18">
+      <c r="B130" s="20" t="n"/>
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="19" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="21" t="n"/>
+      <c r="H130" s="21" t="n"/>
+      <c r="I130" s="8" t="n"/>
+      <c r="J130" s="8" t="n"/>
+      <c r="K130" s="8" t="n"/>
+      <c r="L130" s="22">
         <f>IF(AND(ISNUMBER(G130),ISNUMBER(H130)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G130&amp;","&amp;H130,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="14" t="n">
+      <c r="A131" s="19" t="n">
         <v>129</v>
       </c>
-      <c r="B131" s="15" t="n"/>
-      <c r="C131" s="16" t="n"/>
-      <c r="D131" s="16" t="n"/>
-      <c r="E131" s="14" t="n"/>
-      <c r="F131" s="16" t="n"/>
-      <c r="G131" s="17" t="n"/>
-      <c r="H131" s="17" t="n"/>
-      <c r="I131" s="16" t="n"/>
-      <c r="J131" s="16" t="n"/>
-      <c r="K131" s="16" t="n"/>
-      <c r="L131" s="18">
+      <c r="B131" s="20" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="19" t="n"/>
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="21" t="n"/>
+      <c r="H131" s="21" t="n"/>
+      <c r="I131" s="8" t="n"/>
+      <c r="J131" s="8" t="n"/>
+      <c r="K131" s="8" t="n"/>
+      <c r="L131" s="22">
         <f>IF(AND(ISNUMBER(G131),ISNUMBER(H131)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G131&amp;","&amp;H131,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="14" t="n">
+      <c r="A132" s="19" t="n">
         <v>130</v>
       </c>
-      <c r="B132" s="15" t="n"/>
-      <c r="C132" s="16" t="n"/>
-      <c r="D132" s="16" t="n"/>
-      <c r="E132" s="14" t="n"/>
-      <c r="F132" s="16" t="n"/>
-      <c r="G132" s="17" t="n"/>
-      <c r="H132" s="17" t="n"/>
-      <c r="I132" s="16" t="n"/>
-      <c r="J132" s="16" t="n"/>
-      <c r="K132" s="16" t="n"/>
-      <c r="L132" s="18">
+      <c r="B132" s="20" t="n"/>
+      <c r="C132" s="8" t="n"/>
+      <c r="D132" s="8" t="n"/>
+      <c r="E132" s="19" t="n"/>
+      <c r="F132" s="8" t="n"/>
+      <c r="G132" s="21" t="n"/>
+      <c r="H132" s="21" t="n"/>
+      <c r="I132" s="8" t="n"/>
+      <c r="J132" s="8" t="n"/>
+      <c r="K132" s="8" t="n"/>
+      <c r="L132" s="22">
         <f>IF(AND(ISNUMBER(G132),ISNUMBER(H132)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G132&amp;","&amp;H132,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="14" t="n">
+      <c r="A133" s="19" t="n">
         <v>131</v>
       </c>
-      <c r="B133" s="15" t="n"/>
-      <c r="C133" s="16" t="n"/>
-      <c r="D133" s="16" t="n"/>
-      <c r="E133" s="14" t="n"/>
-      <c r="F133" s="16" t="n"/>
-      <c r="G133" s="17" t="n"/>
-      <c r="H133" s="17" t="n"/>
-      <c r="I133" s="16" t="n"/>
-      <c r="J133" s="16" t="n"/>
-      <c r="K133" s="16" t="n"/>
-      <c r="L133" s="18">
+      <c r="B133" s="20" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="19" t="n"/>
+      <c r="F133" s="8" t="n"/>
+      <c r="G133" s="21" t="n"/>
+      <c r="H133" s="21" t="n"/>
+      <c r="I133" s="8" t="n"/>
+      <c r="J133" s="8" t="n"/>
+      <c r="K133" s="8" t="n"/>
+      <c r="L133" s="22">
         <f>IF(AND(ISNUMBER(G133),ISNUMBER(H133)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G133&amp;","&amp;H133,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="14" t="n">
+      <c r="A134" s="19" t="n">
         <v>132</v>
       </c>
-      <c r="B134" s="15" t="n"/>
-      <c r="C134" s="16" t="n"/>
-      <c r="D134" s="16" t="n"/>
-      <c r="E134" s="14" t="n"/>
-      <c r="F134" s="16" t="n"/>
-      <c r="G134" s="17" t="n"/>
-      <c r="H134" s="17" t="n"/>
-      <c r="I134" s="16" t="n"/>
-      <c r="J134" s="16" t="n"/>
-      <c r="K134" s="16" t="n"/>
-      <c r="L134" s="18">
+      <c r="B134" s="20" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="19" t="n"/>
+      <c r="F134" s="8" t="n"/>
+      <c r="G134" s="21" t="n"/>
+      <c r="H134" s="21" t="n"/>
+      <c r="I134" s="8" t="n"/>
+      <c r="J134" s="8" t="n"/>
+      <c r="K134" s="8" t="n"/>
+      <c r="L134" s="22">
         <f>IF(AND(ISNUMBER(G134),ISNUMBER(H134)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G134&amp;","&amp;H134,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="14" t="n">
+      <c r="A135" s="19" t="n">
         <v>133</v>
       </c>
-      <c r="B135" s="15" t="n"/>
-      <c r="C135" s="16" t="n"/>
-      <c r="D135" s="16" t="n"/>
-      <c r="E135" s="14" t="n"/>
-      <c r="F135" s="16" t="n"/>
-      <c r="G135" s="17" t="n"/>
-      <c r="H135" s="17" t="n"/>
-      <c r="I135" s="16" t="n"/>
-      <c r="J135" s="16" t="n"/>
-      <c r="K135" s="16" t="n"/>
-      <c r="L135" s="18">
+      <c r="B135" s="20" t="n"/>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="19" t="n"/>
+      <c r="F135" s="8" t="n"/>
+      <c r="G135" s="21" t="n"/>
+      <c r="H135" s="21" t="n"/>
+      <c r="I135" s="8" t="n"/>
+      <c r="J135" s="8" t="n"/>
+      <c r="K135" s="8" t="n"/>
+      <c r="L135" s="22">
         <f>IF(AND(ISNUMBER(G135),ISNUMBER(H135)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G135&amp;","&amp;H135,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="14" t="n">
+      <c r="A136" s="19" t="n">
         <v>134</v>
       </c>
-      <c r="B136" s="15" t="n"/>
-      <c r="C136" s="16" t="n"/>
-      <c r="D136" s="16" t="n"/>
-      <c r="E136" s="14" t="n"/>
-      <c r="F136" s="16" t="n"/>
-      <c r="G136" s="17" t="n"/>
-      <c r="H136" s="17" t="n"/>
-      <c r="I136" s="16" t="n"/>
-      <c r="J136" s="16" t="n"/>
-      <c r="K136" s="16" t="n"/>
-      <c r="L136" s="18">
+      <c r="B136" s="20" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="19" t="n"/>
+      <c r="F136" s="8" t="n"/>
+      <c r="G136" s="21" t="n"/>
+      <c r="H136" s="21" t="n"/>
+      <c r="I136" s="8" t="n"/>
+      <c r="J136" s="8" t="n"/>
+      <c r="K136" s="8" t="n"/>
+      <c r="L136" s="22">
         <f>IF(AND(ISNUMBER(G136),ISNUMBER(H136)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G136&amp;","&amp;H136,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="14" t="n">
+      <c r="A137" s="19" t="n">
         <v>135</v>
       </c>
-      <c r="B137" s="15" t="n"/>
-      <c r="C137" s="16" t="n"/>
-      <c r="D137" s="16" t="n"/>
-      <c r="E137" s="14" t="n"/>
-      <c r="F137" s="16" t="n"/>
-      <c r="G137" s="17" t="n"/>
-      <c r="H137" s="17" t="n"/>
-      <c r="I137" s="16" t="n"/>
-      <c r="J137" s="16" t="n"/>
-      <c r="K137" s="16" t="n"/>
-      <c r="L137" s="18">
+      <c r="B137" s="20" t="n"/>
+      <c r="C137" s="8" t="n"/>
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="19" t="n"/>
+      <c r="F137" s="8" t="n"/>
+      <c r="G137" s="21" t="n"/>
+      <c r="H137" s="21" t="n"/>
+      <c r="I137" s="8" t="n"/>
+      <c r="J137" s="8" t="n"/>
+      <c r="K137" s="8" t="n"/>
+      <c r="L137" s="22">
         <f>IF(AND(ISNUMBER(G137),ISNUMBER(H137)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G137&amp;","&amp;H137,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="14" t="n">
+      <c r="A138" s="19" t="n">
         <v>136</v>
       </c>
-      <c r="B138" s="15" t="n"/>
-      <c r="C138" s="16" t="n"/>
-      <c r="D138" s="16" t="n"/>
-      <c r="E138" s="14" t="n"/>
-      <c r="F138" s="16" t="n"/>
-      <c r="G138" s="17" t="n"/>
-      <c r="H138" s="17" t="n"/>
-      <c r="I138" s="16" t="n"/>
-      <c r="J138" s="16" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="18">
+      <c r="B138" s="20" t="n"/>
+      <c r="C138" s="8" t="n"/>
+      <c r="D138" s="8" t="n"/>
+      <c r="E138" s="19" t="n"/>
+      <c r="F138" s="8" t="n"/>
+      <c r="G138" s="21" t="n"/>
+      <c r="H138" s="21" t="n"/>
+      <c r="I138" s="8" t="n"/>
+      <c r="J138" s="8" t="n"/>
+      <c r="K138" s="8" t="n"/>
+      <c r="L138" s="22">
         <f>IF(AND(ISNUMBER(G138),ISNUMBER(H138)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G138&amp;","&amp;H138,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="14" t="n">
+      <c r="A139" s="19" t="n">
         <v>137</v>
       </c>
-      <c r="B139" s="15" t="n"/>
-      <c r="C139" s="16" t="n"/>
-      <c r="D139" s="16" t="n"/>
-      <c r="E139" s="14" t="n"/>
-      <c r="F139" s="16" t="n"/>
-      <c r="G139" s="17" t="n"/>
-      <c r="H139" s="17" t="n"/>
-      <c r="I139" s="16" t="n"/>
-      <c r="J139" s="16" t="n"/>
-      <c r="K139" s="16" t="n"/>
-      <c r="L139" s="18">
+      <c r="B139" s="20" t="n"/>
+      <c r="C139" s="8" t="n"/>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="19" t="n"/>
+      <c r="F139" s="8" t="n"/>
+      <c r="G139" s="21" t="n"/>
+      <c r="H139" s="21" t="n"/>
+      <c r="I139" s="8" t="n"/>
+      <c r="J139" s="8" t="n"/>
+      <c r="K139" s="8" t="n"/>
+      <c r="L139" s="22">
         <f>IF(AND(ISNUMBER(G139),ISNUMBER(H139)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G139&amp;","&amp;H139,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="14" t="n">
+      <c r="A140" s="19" t="n">
         <v>138</v>
       </c>
-      <c r="B140" s="15" t="n"/>
-      <c r="C140" s="16" t="n"/>
-      <c r="D140" s="16" t="n"/>
-      <c r="E140" s="14" t="n"/>
-      <c r="F140" s="16" t="n"/>
-      <c r="G140" s="17" t="n"/>
-      <c r="H140" s="17" t="n"/>
-      <c r="I140" s="16" t="n"/>
-      <c r="J140" s="16" t="n"/>
-      <c r="K140" s="16" t="n"/>
-      <c r="L140" s="18">
+      <c r="B140" s="20" t="n"/>
+      <c r="C140" s="8" t="n"/>
+      <c r="D140" s="8" t="n"/>
+      <c r="E140" s="19" t="n"/>
+      <c r="F140" s="8" t="n"/>
+      <c r="G140" s="21" t="n"/>
+      <c r="H140" s="21" t="n"/>
+      <c r="I140" s="8" t="n"/>
+      <c r="J140" s="8" t="n"/>
+      <c r="K140" s="8" t="n"/>
+      <c r="L140" s="22">
         <f>IF(AND(ISNUMBER(G140),ISNUMBER(H140)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G140&amp;","&amp;H140,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="14" t="n">
+      <c r="A141" s="19" t="n">
         <v>139</v>
       </c>
-      <c r="B141" s="15" t="n"/>
-      <c r="C141" s="16" t="n"/>
-      <c r="D141" s="16" t="n"/>
-      <c r="E141" s="14" t="n"/>
-      <c r="F141" s="16" t="n"/>
-      <c r="G141" s="17" t="n"/>
-      <c r="H141" s="17" t="n"/>
-      <c r="I141" s="16" t="n"/>
-      <c r="J141" s="16" t="n"/>
-      <c r="K141" s="16" t="n"/>
-      <c r="L141" s="18">
+      <c r="B141" s="20" t="n"/>
+      <c r="C141" s="8" t="n"/>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="19" t="n"/>
+      <c r="F141" s="8" t="n"/>
+      <c r="G141" s="21" t="n"/>
+      <c r="H141" s="21" t="n"/>
+      <c r="I141" s="8" t="n"/>
+      <c r="J141" s="8" t="n"/>
+      <c r="K141" s="8" t="n"/>
+      <c r="L141" s="22">
         <f>IF(AND(ISNUMBER(G141),ISNUMBER(H141)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G141&amp;","&amp;H141,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="14" t="n">
+      <c r="A142" s="19" t="n">
         <v>140</v>
       </c>
-      <c r="B142" s="15" t="n"/>
-      <c r="C142" s="16" t="n"/>
-      <c r="D142" s="16" t="n"/>
-      <c r="E142" s="14" t="n"/>
-      <c r="F142" s="16" t="n"/>
-      <c r="G142" s="17" t="n"/>
-      <c r="H142" s="17" t="n"/>
-      <c r="I142" s="16" t="n"/>
-      <c r="J142" s="16" t="n"/>
-      <c r="K142" s="16" t="n"/>
-      <c r="L142" s="18">
+      <c r="B142" s="20" t="n"/>
+      <c r="C142" s="8" t="n"/>
+      <c r="D142" s="8" t="n"/>
+      <c r="E142" s="19" t="n"/>
+      <c r="F142" s="8" t="n"/>
+      <c r="G142" s="21" t="n"/>
+      <c r="H142" s="21" t="n"/>
+      <c r="I142" s="8" t="n"/>
+      <c r="J142" s="8" t="n"/>
+      <c r="K142" s="8" t="n"/>
+      <c r="L142" s="22">
         <f>IF(AND(ISNUMBER(G142),ISNUMBER(H142)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G142&amp;","&amp;H142,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="14" t="n">
+      <c r="A143" s="19" t="n">
         <v>141</v>
       </c>
-      <c r="B143" s="15" t="n"/>
-      <c r="C143" s="16" t="n"/>
-      <c r="D143" s="16" t="n"/>
-      <c r="E143" s="14" t="n"/>
-      <c r="F143" s="16" t="n"/>
-      <c r="G143" s="17" t="n"/>
-      <c r="H143" s="17" t="n"/>
-      <c r="I143" s="16" t="n"/>
-      <c r="J143" s="16" t="n"/>
-      <c r="K143" s="16" t="n"/>
-      <c r="L143" s="18">
+      <c r="B143" s="20" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="19" t="n"/>
+      <c r="F143" s="8" t="n"/>
+      <c r="G143" s="21" t="n"/>
+      <c r="H143" s="21" t="n"/>
+      <c r="I143" s="8" t="n"/>
+      <c r="J143" s="8" t="n"/>
+      <c r="K143" s="8" t="n"/>
+      <c r="L143" s="22">
         <f>IF(AND(ISNUMBER(G143),ISNUMBER(H143)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G143&amp;","&amp;H143,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="14" t="n">
+      <c r="A144" s="19" t="n">
         <v>142</v>
       </c>
-      <c r="B144" s="15" t="n"/>
-      <c r="C144" s="16" t="n"/>
-      <c r="D144" s="16" t="n"/>
-      <c r="E144" s="14" t="n"/>
-      <c r="F144" s="16" t="n"/>
-      <c r="G144" s="17" t="n"/>
-      <c r="H144" s="17" t="n"/>
-      <c r="I144" s="16" t="n"/>
-      <c r="J144" s="16" t="n"/>
-      <c r="K144" s="16" t="n"/>
-      <c r="L144" s="18">
+      <c r="B144" s="20" t="n"/>
+      <c r="C144" s="8" t="n"/>
+      <c r="D144" s="8" t="n"/>
+      <c r="E144" s="19" t="n"/>
+      <c r="F144" s="8" t="n"/>
+      <c r="G144" s="21" t="n"/>
+      <c r="H144" s="21" t="n"/>
+      <c r="I144" s="8" t="n"/>
+      <c r="J144" s="8" t="n"/>
+      <c r="K144" s="8" t="n"/>
+      <c r="L144" s="22">
         <f>IF(AND(ISNUMBER(G144),ISNUMBER(H144)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G144&amp;","&amp;H144,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="14" t="n">
+      <c r="A145" s="19" t="n">
         <v>143</v>
       </c>
-      <c r="B145" s="15" t="n"/>
-      <c r="C145" s="16" t="n"/>
-      <c r="D145" s="16" t="n"/>
-      <c r="E145" s="14" t="n"/>
-      <c r="F145" s="16" t="n"/>
-      <c r="G145" s="17" t="n"/>
-      <c r="H145" s="17" t="n"/>
-      <c r="I145" s="16" t="n"/>
-      <c r="J145" s="16" t="n"/>
-      <c r="K145" s="16" t="n"/>
-      <c r="L145" s="18">
+      <c r="B145" s="20" t="n"/>
+      <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="19" t="n"/>
+      <c r="F145" s="8" t="n"/>
+      <c r="G145" s="21" t="n"/>
+      <c r="H145" s="21" t="n"/>
+      <c r="I145" s="8" t="n"/>
+      <c r="J145" s="8" t="n"/>
+      <c r="K145" s="8" t="n"/>
+      <c r="L145" s="22">
         <f>IF(AND(ISNUMBER(G145),ISNUMBER(H145)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G145&amp;","&amp;H145,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="14" t="n">
+      <c r="A146" s="19" t="n">
         <v>144</v>
       </c>
-      <c r="B146" s="15" t="n"/>
-      <c r="C146" s="16" t="n"/>
-      <c r="D146" s="16" t="n"/>
-      <c r="E146" s="14" t="n"/>
-      <c r="F146" s="16" t="n"/>
-      <c r="G146" s="17" t="n"/>
-      <c r="H146" s="17" t="n"/>
-      <c r="I146" s="16" t="n"/>
-      <c r="J146" s="16" t="n"/>
-      <c r="K146" s="16" t="n"/>
-      <c r="L146" s="18">
+      <c r="B146" s="20" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="19" t="n"/>
+      <c r="F146" s="8" t="n"/>
+      <c r="G146" s="21" t="n"/>
+      <c r="H146" s="21" t="n"/>
+      <c r="I146" s="8" t="n"/>
+      <c r="J146" s="8" t="n"/>
+      <c r="K146" s="8" t="n"/>
+      <c r="L146" s="22">
         <f>IF(AND(ISNUMBER(G146),ISNUMBER(H146)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G146&amp;","&amp;H146,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="14" t="n">
+      <c r="A147" s="19" t="n">
         <v>145</v>
       </c>
-      <c r="B147" s="15" t="n"/>
-      <c r="C147" s="16" t="n"/>
-      <c r="D147" s="16" t="n"/>
-      <c r="E147" s="14" t="n"/>
-      <c r="F147" s="16" t="n"/>
-      <c r="G147" s="17" t="n"/>
-      <c r="H147" s="17" t="n"/>
-      <c r="I147" s="16" t="n"/>
-      <c r="J147" s="16" t="n"/>
-      <c r="K147" s="16" t="n"/>
-      <c r="L147" s="18">
+      <c r="B147" s="20" t="n"/>
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="19" t="n"/>
+      <c r="F147" s="8" t="n"/>
+      <c r="G147" s="21" t="n"/>
+      <c r="H147" s="21" t="n"/>
+      <c r="I147" s="8" t="n"/>
+      <c r="J147" s="8" t="n"/>
+      <c r="K147" s="8" t="n"/>
+      <c r="L147" s="22">
         <f>IF(AND(ISNUMBER(G147),ISNUMBER(H147)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G147&amp;","&amp;H147,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="14" t="n">
+      <c r="A148" s="19" t="n">
         <v>146</v>
       </c>
-      <c r="B148" s="15" t="n"/>
-      <c r="C148" s="16" t="n"/>
-      <c r="D148" s="16" t="n"/>
-      <c r="E148" s="14" t="n"/>
-      <c r="F148" s="16" t="n"/>
-      <c r="G148" s="17" t="n"/>
-      <c r="H148" s="17" t="n"/>
-      <c r="I148" s="16" t="n"/>
-      <c r="J148" s="16" t="n"/>
-      <c r="K148" s="16" t="n"/>
-      <c r="L148" s="18">
+      <c r="B148" s="20" t="n"/>
+      <c r="C148" s="8" t="n"/>
+      <c r="D148" s="8" t="n"/>
+      <c r="E148" s="19" t="n"/>
+      <c r="F148" s="8" t="n"/>
+      <c r="G148" s="21" t="n"/>
+      <c r="H148" s="21" t="n"/>
+      <c r="I148" s="8" t="n"/>
+      <c r="J148" s="8" t="n"/>
+      <c r="K148" s="8" t="n"/>
+      <c r="L148" s="22">
         <f>IF(AND(ISNUMBER(G148),ISNUMBER(H148)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G148&amp;","&amp;H148,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="14" t="n">
+      <c r="A149" s="19" t="n">
         <v>147</v>
       </c>
-      <c r="B149" s="15" t="n"/>
-      <c r="C149" s="16" t="n"/>
-      <c r="D149" s="16" t="n"/>
-      <c r="E149" s="14" t="n"/>
-      <c r="F149" s="16" t="n"/>
-      <c r="G149" s="17" t="n"/>
-      <c r="H149" s="17" t="n"/>
-      <c r="I149" s="16" t="n"/>
-      <c r="J149" s="16" t="n"/>
-      <c r="K149" s="16" t="n"/>
-      <c r="L149" s="18">
+      <c r="B149" s="20" t="n"/>
+      <c r="C149" s="8" t="n"/>
+      <c r="D149" s="8" t="n"/>
+      <c r="E149" s="19" t="n"/>
+      <c r="F149" s="8" t="n"/>
+      <c r="G149" s="21" t="n"/>
+      <c r="H149" s="21" t="n"/>
+      <c r="I149" s="8" t="n"/>
+      <c r="J149" s="8" t="n"/>
+      <c r="K149" s="8" t="n"/>
+      <c r="L149" s="22">
         <f>IF(AND(ISNUMBER(G149),ISNUMBER(H149)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G149&amp;","&amp;H149,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="14" t="n">
+      <c r="A150" s="19" t="n">
         <v>148</v>
       </c>
-      <c r="B150" s="15" t="n"/>
-      <c r="C150" s="16" t="n"/>
-      <c r="D150" s="16" t="n"/>
-      <c r="E150" s="14" t="n"/>
-      <c r="F150" s="16" t="n"/>
-      <c r="G150" s="17" t="n"/>
-      <c r="H150" s="17" t="n"/>
-      <c r="I150" s="16" t="n"/>
-      <c r="J150" s="16" t="n"/>
-      <c r="K150" s="16" t="n"/>
-      <c r="L150" s="18">
+      <c r="B150" s="20" t="n"/>
+      <c r="C150" s="8" t="n"/>
+      <c r="D150" s="8" t="n"/>
+      <c r="E150" s="19" t="n"/>
+      <c r="F150" s="8" t="n"/>
+      <c r="G150" s="21" t="n"/>
+      <c r="H150" s="21" t="n"/>
+      <c r="I150" s="8" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="8" t="n"/>
+      <c r="L150" s="22">
         <f>IF(AND(ISNUMBER(G150),ISNUMBER(H150)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G150&amp;","&amp;H150,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="14" t="n">
+      <c r="A151" s="19" t="n">
         <v>149</v>
       </c>
-      <c r="B151" s="15" t="n"/>
-      <c r="C151" s="16" t="n"/>
-      <c r="D151" s="16" t="n"/>
-      <c r="E151" s="14" t="n"/>
-      <c r="F151" s="16" t="n"/>
-      <c r="G151" s="17" t="n"/>
-      <c r="H151" s="17" t="n"/>
-      <c r="I151" s="16" t="n"/>
-      <c r="J151" s="16" t="n"/>
-      <c r="K151" s="16" t="n"/>
-      <c r="L151" s="18">
+      <c r="B151" s="20" t="n"/>
+      <c r="C151" s="8" t="n"/>
+      <c r="D151" s="8" t="n"/>
+      <c r="E151" s="19" t="n"/>
+      <c r="F151" s="8" t="n"/>
+      <c r="G151" s="21" t="n"/>
+      <c r="H151" s="21" t="n"/>
+      <c r="I151" s="8" t="n"/>
+      <c r="J151" s="8" t="n"/>
+      <c r="K151" s="8" t="n"/>
+      <c r="L151" s="22">
         <f>IF(AND(ISNUMBER(G151),ISNUMBER(H151)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G151&amp;","&amp;H151,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="14" t="n">
+      <c r="A152" s="19" t="n">
         <v>150</v>
       </c>
-      <c r="B152" s="15" t="n"/>
-      <c r="C152" s="16" t="n"/>
-      <c r="D152" s="16" t="n"/>
-      <c r="E152" s="14" t="n"/>
-      <c r="F152" s="16" t="n"/>
-      <c r="G152" s="17" t="n"/>
-      <c r="H152" s="17" t="n"/>
-      <c r="I152" s="16" t="n"/>
-      <c r="J152" s="16" t="n"/>
-      <c r="K152" s="16" t="n"/>
-      <c r="L152" s="18">
+      <c r="B152" s="20" t="n"/>
+      <c r="C152" s="8" t="n"/>
+      <c r="D152" s="8" t="n"/>
+      <c r="E152" s="19" t="n"/>
+      <c r="F152" s="8" t="n"/>
+      <c r="G152" s="21" t="n"/>
+      <c r="H152" s="21" t="n"/>
+      <c r="I152" s="8" t="n"/>
+      <c r="J152" s="8" t="n"/>
+      <c r="K152" s="8" t="n"/>
+      <c r="L152" s="22">
         <f>IF(AND(ISNUMBER(G152),ISNUMBER(H152)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G152&amp;","&amp;H152,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="14" t="n">
+      <c r="A153" s="19" t="n">
         <v>151</v>
       </c>
-      <c r="B153" s="15" t="n"/>
-      <c r="C153" s="16" t="n"/>
-      <c r="D153" s="16" t="n"/>
-      <c r="E153" s="14" t="n"/>
-      <c r="F153" s="16" t="n"/>
-      <c r="G153" s="17" t="n"/>
-      <c r="H153" s="17" t="n"/>
-      <c r="I153" s="16" t="n"/>
-      <c r="J153" s="16" t="n"/>
-      <c r="K153" s="16" t="n"/>
-      <c r="L153" s="18">
+      <c r="B153" s="20" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="19" t="n"/>
+      <c r="F153" s="8" t="n"/>
+      <c r="G153" s="21" t="n"/>
+      <c r="H153" s="21" t="n"/>
+      <c r="I153" s="8" t="n"/>
+      <c r="J153" s="8" t="n"/>
+      <c r="K153" s="8" t="n"/>
+      <c r="L153" s="22">
         <f>IF(AND(ISNUMBER(G153),ISNUMBER(H153)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G153&amp;","&amp;H153,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="14" t="n">
+      <c r="A154" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="B154" s="15" t="n"/>
-      <c r="C154" s="16" t="n"/>
-      <c r="D154" s="16" t="n"/>
-      <c r="E154" s="14" t="n"/>
-      <c r="F154" s="16" t="n"/>
-      <c r="G154" s="17" t="n"/>
-      <c r="H154" s="17" t="n"/>
-      <c r="I154" s="16" t="n"/>
-      <c r="J154" s="16" t="n"/>
-      <c r="K154" s="16" t="n"/>
-      <c r="L154" s="18">
+      <c r="B154" s="20" t="n"/>
+      <c r="C154" s="8" t="n"/>
+      <c r="D154" s="8" t="n"/>
+      <c r="E154" s="19" t="n"/>
+      <c r="F154" s="8" t="n"/>
+      <c r="G154" s="21" t="n"/>
+      <c r="H154" s="21" t="n"/>
+      <c r="I154" s="8" t="n"/>
+      <c r="J154" s="8" t="n"/>
+      <c r="K154" s="8" t="n"/>
+      <c r="L154" s="22">
         <f>IF(AND(ISNUMBER(G154),ISNUMBER(H154)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G154&amp;","&amp;H154,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="14" t="n">
+      <c r="A155" s="19" t="n">
         <v>153</v>
       </c>
-      <c r="B155" s="15" t="n"/>
-      <c r="C155" s="16" t="n"/>
-      <c r="D155" s="16" t="n"/>
-      <c r="E155" s="14" t="n"/>
-      <c r="F155" s="16" t="n"/>
-      <c r="G155" s="17" t="n"/>
-      <c r="H155" s="17" t="n"/>
-      <c r="I155" s="16" t="n"/>
-      <c r="J155" s="16" t="n"/>
-      <c r="K155" s="16" t="n"/>
-      <c r="L155" s="18">
+      <c r="B155" s="20" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="19" t="n"/>
+      <c r="F155" s="8" t="n"/>
+      <c r="G155" s="21" t="n"/>
+      <c r="H155" s="21" t="n"/>
+      <c r="I155" s="8" t="n"/>
+      <c r="J155" s="8" t="n"/>
+      <c r="K155" s="8" t="n"/>
+      <c r="L155" s="22">
         <f>IF(AND(ISNUMBER(G155),ISNUMBER(H155)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G155&amp;","&amp;H155,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="14" t="n">
+      <c r="A156" s="19" t="n">
         <v>154</v>
       </c>
-      <c r="B156" s="15" t="n"/>
-      <c r="C156" s="16" t="n"/>
-      <c r="D156" s="16" t="n"/>
-      <c r="E156" s="14" t="n"/>
-      <c r="F156" s="16" t="n"/>
-      <c r="G156" s="17" t="n"/>
-      <c r="H156" s="17" t="n"/>
-      <c r="I156" s="16" t="n"/>
-      <c r="J156" s="16" t="n"/>
-      <c r="K156" s="16" t="n"/>
-      <c r="L156" s="18">
+      <c r="B156" s="20" t="n"/>
+      <c r="C156" s="8" t="n"/>
+      <c r="D156" s="8" t="n"/>
+      <c r="E156" s="19" t="n"/>
+      <c r="F156" s="8" t="n"/>
+      <c r="G156" s="21" t="n"/>
+      <c r="H156" s="21" t="n"/>
+      <c r="I156" s="8" t="n"/>
+      <c r="J156" s="8" t="n"/>
+      <c r="K156" s="8" t="n"/>
+      <c r="L156" s="22">
         <f>IF(AND(ISNUMBER(G156),ISNUMBER(H156)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G156&amp;","&amp;H156,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="14" t="n">
+      <c r="A157" s="19" t="n">
         <v>155</v>
       </c>
-      <c r="B157" s="15" t="n"/>
-      <c r="C157" s="16" t="n"/>
-      <c r="D157" s="16" t="n"/>
-      <c r="E157" s="14" t="n"/>
-      <c r="F157" s="16" t="n"/>
-      <c r="G157" s="17" t="n"/>
-      <c r="H157" s="17" t="n"/>
-      <c r="I157" s="16" t="n"/>
-      <c r="J157" s="16" t="n"/>
-      <c r="K157" s="16" t="n"/>
-      <c r="L157" s="18">
+      <c r="B157" s="20" t="n"/>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="19" t="n"/>
+      <c r="F157" s="8" t="n"/>
+      <c r="G157" s="21" t="n"/>
+      <c r="H157" s="21" t="n"/>
+      <c r="I157" s="8" t="n"/>
+      <c r="J157" s="8" t="n"/>
+      <c r="K157" s="8" t="n"/>
+      <c r="L157" s="22">
         <f>IF(AND(ISNUMBER(G157),ISNUMBER(H157)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G157&amp;","&amp;H157,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="14" t="n">
+      <c r="A158" s="19" t="n">
         <v>156</v>
       </c>
-      <c r="B158" s="15" t="n"/>
-      <c r="C158" s="16" t="n"/>
-      <c r="D158" s="16" t="n"/>
-      <c r="E158" s="14" t="n"/>
-      <c r="F158" s="16" t="n"/>
-      <c r="G158" s="17" t="n"/>
-      <c r="H158" s="17" t="n"/>
-      <c r="I158" s="16" t="n"/>
-      <c r="J158" s="16" t="n"/>
-      <c r="K158" s="16" t="n"/>
-      <c r="L158" s="18">
+      <c r="B158" s="20" t="n"/>
+      <c r="C158" s="8" t="n"/>
+      <c r="D158" s="8" t="n"/>
+      <c r="E158" s="19" t="n"/>
+      <c r="F158" s="8" t="n"/>
+      <c r="G158" s="21" t="n"/>
+      <c r="H158" s="21" t="n"/>
+      <c r="I158" s="8" t="n"/>
+      <c r="J158" s="8" t="n"/>
+      <c r="K158" s="8" t="n"/>
+      <c r="L158" s="22">
         <f>IF(AND(ISNUMBER(G158),ISNUMBER(H158)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G158&amp;","&amp;H158,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="14" t="n">
+      <c r="A159" s="19" t="n">
         <v>157</v>
       </c>
-      <c r="B159" s="15" t="n"/>
-      <c r="C159" s="16" t="n"/>
-      <c r="D159" s="16" t="n"/>
-      <c r="E159" s="14" t="n"/>
-      <c r="F159" s="16" t="n"/>
-      <c r="G159" s="17" t="n"/>
-      <c r="H159" s="17" t="n"/>
-      <c r="I159" s="16" t="n"/>
-      <c r="J159" s="16" t="n"/>
-      <c r="K159" s="16" t="n"/>
-      <c r="L159" s="18">
+      <c r="B159" s="20" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="19" t="n"/>
+      <c r="F159" s="8" t="n"/>
+      <c r="G159" s="21" t="n"/>
+      <c r="H159" s="21" t="n"/>
+      <c r="I159" s="8" t="n"/>
+      <c r="J159" s="8" t="n"/>
+      <c r="K159" s="8" t="n"/>
+      <c r="L159" s="22">
         <f>IF(AND(ISNUMBER(G159),ISNUMBER(H159)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G159&amp;","&amp;H159,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="14" t="n">
+      <c r="A160" s="19" t="n">
         <v>158</v>
       </c>
-      <c r="B160" s="15" t="n"/>
-      <c r="C160" s="16" t="n"/>
-      <c r="D160" s="16" t="n"/>
-      <c r="E160" s="14" t="n"/>
-      <c r="F160" s="16" t="n"/>
-      <c r="G160" s="17" t="n"/>
-      <c r="H160" s="17" t="n"/>
-      <c r="I160" s="16" t="n"/>
-      <c r="J160" s="16" t="n"/>
-      <c r="K160" s="16" t="n"/>
-      <c r="L160" s="18">
+      <c r="B160" s="20" t="n"/>
+      <c r="C160" s="8" t="n"/>
+      <c r="D160" s="8" t="n"/>
+      <c r="E160" s="19" t="n"/>
+      <c r="F160" s="8" t="n"/>
+      <c r="G160" s="21" t="n"/>
+      <c r="H160" s="21" t="n"/>
+      <c r="I160" s="8" t="n"/>
+      <c r="J160" s="8" t="n"/>
+      <c r="K160" s="8" t="n"/>
+      <c r="L160" s="22">
         <f>IF(AND(ISNUMBER(G160),ISNUMBER(H160)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G160&amp;","&amp;H160,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="14" t="n">
+      <c r="A161" s="19" t="n">
         <v>159</v>
       </c>
-      <c r="B161" s="15" t="n"/>
-      <c r="C161" s="16" t="n"/>
-      <c r="D161" s="16" t="n"/>
-      <c r="E161" s="14" t="n"/>
-      <c r="F161" s="16" t="n"/>
-      <c r="G161" s="17" t="n"/>
-      <c r="H161" s="17" t="n"/>
-      <c r="I161" s="16" t="n"/>
-      <c r="J161" s="16" t="n"/>
-      <c r="K161" s="16" t="n"/>
-      <c r="L161" s="18">
+      <c r="B161" s="20" t="n"/>
+      <c r="C161" s="8" t="n"/>
+      <c r="D161" s="8" t="n"/>
+      <c r="E161" s="19" t="n"/>
+      <c r="F161" s="8" t="n"/>
+      <c r="G161" s="21" t="n"/>
+      <c r="H161" s="21" t="n"/>
+      <c r="I161" s="8" t="n"/>
+      <c r="J161" s="8" t="n"/>
+      <c r="K161" s="8" t="n"/>
+      <c r="L161" s="22">
         <f>IF(AND(ISNUMBER(G161),ISNUMBER(H161)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G161&amp;","&amp;H161,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="14" t="n">
+      <c r="A162" s="19" t="n">
         <v>160</v>
       </c>
-      <c r="B162" s="15" t="n"/>
-      <c r="C162" s="16" t="n"/>
-      <c r="D162" s="16" t="n"/>
-      <c r="E162" s="14" t="n"/>
-      <c r="F162" s="16" t="n"/>
-      <c r="G162" s="17" t="n"/>
-      <c r="H162" s="17" t="n"/>
-      <c r="I162" s="16" t="n"/>
-      <c r="J162" s="16" t="n"/>
-      <c r="K162" s="16" t="n"/>
-      <c r="L162" s="18">
+      <c r="B162" s="20" t="n"/>
+      <c r="C162" s="8" t="n"/>
+      <c r="D162" s="8" t="n"/>
+      <c r="E162" s="19" t="n"/>
+      <c r="F162" s="8" t="n"/>
+      <c r="G162" s="21" t="n"/>
+      <c r="H162" s="21" t="n"/>
+      <c r="I162" s="8" t="n"/>
+      <c r="J162" s="8" t="n"/>
+      <c r="K162" s="8" t="n"/>
+      <c r="L162" s="22">
         <f>IF(AND(ISNUMBER(G162),ISNUMBER(H162)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G162&amp;","&amp;H162,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="14" t="n">
+      <c r="A163" s="19" t="n">
         <v>161</v>
       </c>
-      <c r="B163" s="15" t="n"/>
-      <c r="C163" s="16" t="n"/>
-      <c r="D163" s="16" t="n"/>
-      <c r="E163" s="14" t="n"/>
-      <c r="F163" s="16" t="n"/>
-      <c r="G163" s="17" t="n"/>
-      <c r="H163" s="17" t="n"/>
-      <c r="I163" s="16" t="n"/>
-      <c r="J163" s="16" t="n"/>
-      <c r="K163" s="16" t="n"/>
-      <c r="L163" s="18">
+      <c r="B163" s="20" t="n"/>
+      <c r="C163" s="8" t="n"/>
+      <c r="D163" s="8" t="n"/>
+      <c r="E163" s="19" t="n"/>
+      <c r="F163" s="8" t="n"/>
+      <c r="G163" s="21" t="n"/>
+      <c r="H163" s="21" t="n"/>
+      <c r="I163" s="8" t="n"/>
+      <c r="J163" s="8" t="n"/>
+      <c r="K163" s="8" t="n"/>
+      <c r="L163" s="22">
         <f>IF(AND(ISNUMBER(G163),ISNUMBER(H163)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G163&amp;","&amp;H163,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="14" t="n">
+      <c r="A164" s="19" t="n">
         <v>162</v>
       </c>
-      <c r="B164" s="15" t="n"/>
-      <c r="C164" s="16" t="n"/>
-      <c r="D164" s="16" t="n"/>
-      <c r="E164" s="14" t="n"/>
-      <c r="F164" s="16" t="n"/>
-      <c r="G164" s="17" t="n"/>
-      <c r="H164" s="17" t="n"/>
-      <c r="I164" s="16" t="n"/>
-      <c r="J164" s="16" t="n"/>
-      <c r="K164" s="16" t="n"/>
-      <c r="L164" s="18">
+      <c r="B164" s="20" t="n"/>
+      <c r="C164" s="8" t="n"/>
+      <c r="D164" s="8" t="n"/>
+      <c r="E164" s="19" t="n"/>
+      <c r="F164" s="8" t="n"/>
+      <c r="G164" s="21" t="n"/>
+      <c r="H164" s="21" t="n"/>
+      <c r="I164" s="8" t="n"/>
+      <c r="J164" s="8" t="n"/>
+      <c r="K164" s="8" t="n"/>
+      <c r="L164" s="22">
         <f>IF(AND(ISNUMBER(G164),ISNUMBER(H164)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G164&amp;","&amp;H164,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="14" t="n">
+      <c r="A165" s="19" t="n">
         <v>163</v>
       </c>
-      <c r="B165" s="15" t="n"/>
-      <c r="C165" s="16" t="n"/>
-      <c r="D165" s="16" t="n"/>
-      <c r="E165" s="14" t="n"/>
-      <c r="F165" s="16" t="n"/>
-      <c r="G165" s="17" t="n"/>
-      <c r="H165" s="17" t="n"/>
-      <c r="I165" s="16" t="n"/>
-      <c r="J165" s="16" t="n"/>
-      <c r="K165" s="16" t="n"/>
-      <c r="L165" s="18">
+      <c r="B165" s="20" t="n"/>
+      <c r="C165" s="8" t="n"/>
+      <c r="D165" s="8" t="n"/>
+      <c r="E165" s="19" t="n"/>
+      <c r="F165" s="8" t="n"/>
+      <c r="G165" s="21" t="n"/>
+      <c r="H165" s="21" t="n"/>
+      <c r="I165" s="8" t="n"/>
+      <c r="J165" s="8" t="n"/>
+      <c r="K165" s="8" t="n"/>
+      <c r="L165" s="22">
         <f>IF(AND(ISNUMBER(G165),ISNUMBER(H165)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G165&amp;","&amp;H165,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="14" t="n">
+      <c r="A166" s="19" t="n">
         <v>164</v>
       </c>
-      <c r="B166" s="15" t="n"/>
-      <c r="C166" s="16" t="n"/>
-      <c r="D166" s="16" t="n"/>
-      <c r="E166" s="14" t="n"/>
-      <c r="F166" s="16" t="n"/>
-      <c r="G166" s="17" t="n"/>
-      <c r="H166" s="17" t="n"/>
-      <c r="I166" s="16" t="n"/>
-      <c r="J166" s="16" t="n"/>
-      <c r="K166" s="16" t="n"/>
-      <c r="L166" s="18">
+      <c r="B166" s="20" t="n"/>
+      <c r="C166" s="8" t="n"/>
+      <c r="D166" s="8" t="n"/>
+      <c r="E166" s="19" t="n"/>
+      <c r="F166" s="8" t="n"/>
+      <c r="G166" s="21" t="n"/>
+      <c r="H166" s="21" t="n"/>
+      <c r="I166" s="8" t="n"/>
+      <c r="J166" s="8" t="n"/>
+      <c r="K166" s="8" t="n"/>
+      <c r="L166" s="22">
         <f>IF(AND(ISNUMBER(G166),ISNUMBER(H166)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G166&amp;","&amp;H166,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="14" t="n">
+      <c r="A167" s="19" t="n">
         <v>165</v>
       </c>
-      <c r="B167" s="15" t="n"/>
-      <c r="C167" s="16" t="n"/>
-      <c r="D167" s="16" t="n"/>
-      <c r="E167" s="14" t="n"/>
-      <c r="F167" s="16" t="n"/>
-      <c r="G167" s="17" t="n"/>
-      <c r="H167" s="17" t="n"/>
-      <c r="I167" s="16" t="n"/>
-      <c r="J167" s="16" t="n"/>
-      <c r="K167" s="16" t="n"/>
-      <c r="L167" s="18">
+      <c r="B167" s="20" t="n"/>
+      <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="19" t="n"/>
+      <c r="F167" s="8" t="n"/>
+      <c r="G167" s="21" t="n"/>
+      <c r="H167" s="21" t="n"/>
+      <c r="I167" s="8" t="n"/>
+      <c r="J167" s="8" t="n"/>
+      <c r="K167" s="8" t="n"/>
+      <c r="L167" s="22">
         <f>IF(AND(ISNUMBER(G167),ISNUMBER(H167)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G167&amp;","&amp;H167,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="14" t="n">
+      <c r="A168" s="19" t="n">
         <v>166</v>
       </c>
-      <c r="B168" s="15" t="n"/>
-      <c r="C168" s="16" t="n"/>
-      <c r="D168" s="16" t="n"/>
-      <c r="E168" s="14" t="n"/>
-      <c r="F168" s="16" t="n"/>
-      <c r="G168" s="17" t="n"/>
-      <c r="H168" s="17" t="n"/>
-      <c r="I168" s="16" t="n"/>
-      <c r="J168" s="16" t="n"/>
-      <c r="K168" s="16" t="n"/>
-      <c r="L168" s="18">
+      <c r="B168" s="20" t="n"/>
+      <c r="C168" s="8" t="n"/>
+      <c r="D168" s="8" t="n"/>
+      <c r="E168" s="19" t="n"/>
+      <c r="F168" s="8" t="n"/>
+      <c r="G168" s="21" t="n"/>
+      <c r="H168" s="21" t="n"/>
+      <c r="I168" s="8" t="n"/>
+      <c r="J168" s="8" t="n"/>
+      <c r="K168" s="8" t="n"/>
+      <c r="L168" s="22">
         <f>IF(AND(ISNUMBER(G168),ISNUMBER(H168)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G168&amp;","&amp;H168,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="14" t="n">
+      <c r="A169" s="19" t="n">
         <v>167</v>
       </c>
-      <c r="B169" s="15" t="n"/>
-      <c r="C169" s="16" t="n"/>
-      <c r="D169" s="16" t="n"/>
-      <c r="E169" s="14" t="n"/>
-      <c r="F169" s="16" t="n"/>
-      <c r="G169" s="17" t="n"/>
-      <c r="H169" s="17" t="n"/>
-      <c r="I169" s="16" t="n"/>
-      <c r="J169" s="16" t="n"/>
-      <c r="K169" s="16" t="n"/>
-      <c r="L169" s="18">
+      <c r="B169" s="20" t="n"/>
+      <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
+      <c r="E169" s="19" t="n"/>
+      <c r="F169" s="8" t="n"/>
+      <c r="G169" s="21" t="n"/>
+      <c r="H169" s="21" t="n"/>
+      <c r="I169" s="8" t="n"/>
+      <c r="J169" s="8" t="n"/>
+      <c r="K169" s="8" t="n"/>
+      <c r="L169" s="22">
         <f>IF(AND(ISNUMBER(G169),ISNUMBER(H169)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G169&amp;","&amp;H169,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="14" t="n">
+      <c r="A170" s="19" t="n">
         <v>168</v>
       </c>
-      <c r="B170" s="15" t="n"/>
-      <c r="C170" s="16" t="n"/>
-      <c r="D170" s="16" t="n"/>
-      <c r="E170" s="14" t="n"/>
-      <c r="F170" s="16" t="n"/>
-      <c r="G170" s="17" t="n"/>
-      <c r="H170" s="17" t="n"/>
-      <c r="I170" s="16" t="n"/>
-      <c r="J170" s="16" t="n"/>
-      <c r="K170" s="16" t="n"/>
-      <c r="L170" s="18">
+      <c r="B170" s="20" t="n"/>
+      <c r="C170" s="8" t="n"/>
+      <c r="D170" s="8" t="n"/>
+      <c r="E170" s="19" t="n"/>
+      <c r="F170" s="8" t="n"/>
+      <c r="G170" s="21" t="n"/>
+      <c r="H170" s="21" t="n"/>
+      <c r="I170" s="8" t="n"/>
+      <c r="J170" s="8" t="n"/>
+      <c r="K170" s="8" t="n"/>
+      <c r="L170" s="22">
         <f>IF(AND(ISNUMBER(G170),ISNUMBER(H170)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G170&amp;","&amp;H170,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="14" t="n">
+      <c r="A171" s="19" t="n">
         <v>169</v>
       </c>
-      <c r="B171" s="15" t="n"/>
-      <c r="C171" s="16" t="n"/>
-      <c r="D171" s="16" t="n"/>
-      <c r="E171" s="14" t="n"/>
-      <c r="F171" s="16" t="n"/>
-      <c r="G171" s="17" t="n"/>
-      <c r="H171" s="17" t="n"/>
-      <c r="I171" s="16" t="n"/>
-      <c r="J171" s="16" t="n"/>
-      <c r="K171" s="16" t="n"/>
-      <c r="L171" s="18">
+      <c r="B171" s="20" t="n"/>
+      <c r="C171" s="8" t="n"/>
+      <c r="D171" s="8" t="n"/>
+      <c r="E171" s="19" t="n"/>
+      <c r="F171" s="8" t="n"/>
+      <c r="G171" s="21" t="n"/>
+      <c r="H171" s="21" t="n"/>
+      <c r="I171" s="8" t="n"/>
+      <c r="J171" s="8" t="n"/>
+      <c r="K171" s="8" t="n"/>
+      <c r="L171" s="22">
         <f>IF(AND(ISNUMBER(G171),ISNUMBER(H171)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G171&amp;","&amp;H171,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="14" t="n">
+      <c r="A172" s="19" t="n">
         <v>170</v>
       </c>
-      <c r="B172" s="15" t="n"/>
-      <c r="C172" s="16" t="n"/>
-      <c r="D172" s="16" t="n"/>
-      <c r="E172" s="14" t="n"/>
-      <c r="F172" s="16" t="n"/>
-      <c r="G172" s="17" t="n"/>
-      <c r="H172" s="17" t="n"/>
-      <c r="I172" s="16" t="n"/>
-      <c r="J172" s="16" t="n"/>
-      <c r="K172" s="16" t="n"/>
-      <c r="L172" s="18">
+      <c r="B172" s="20" t="n"/>
+      <c r="C172" s="8" t="n"/>
+      <c r="D172" s="8" t="n"/>
+      <c r="E172" s="19" t="n"/>
+      <c r="F172" s="8" t="n"/>
+      <c r="G172" s="21" t="n"/>
+      <c r="H172" s="21" t="n"/>
+      <c r="I172" s="8" t="n"/>
+      <c r="J172" s="8" t="n"/>
+      <c r="K172" s="8" t="n"/>
+      <c r="L172" s="22">
         <f>IF(AND(ISNUMBER(G172),ISNUMBER(H172)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G172&amp;","&amp;H172,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="14" t="n">
+      <c r="A173" s="19" t="n">
         <v>171</v>
       </c>
-      <c r="B173" s="15" t="n"/>
-      <c r="C173" s="16" t="n"/>
-      <c r="D173" s="16" t="n"/>
-      <c r="E173" s="14" t="n"/>
-      <c r="F173" s="16" t="n"/>
-      <c r="G173" s="17" t="n"/>
-      <c r="H173" s="17" t="n"/>
-      <c r="I173" s="16" t="n"/>
-      <c r="J173" s="16" t="n"/>
-      <c r="K173" s="16" t="n"/>
-      <c r="L173" s="18">
+      <c r="B173" s="20" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="19" t="n"/>
+      <c r="F173" s="8" t="n"/>
+      <c r="G173" s="21" t="n"/>
+      <c r="H173" s="21" t="n"/>
+      <c r="I173" s="8" t="n"/>
+      <c r="J173" s="8" t="n"/>
+      <c r="K173" s="8" t="n"/>
+      <c r="L173" s="22">
         <f>IF(AND(ISNUMBER(G173),ISNUMBER(H173)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G173&amp;","&amp;H173,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="14" t="n">
+      <c r="A174" s="19" t="n">
         <v>172</v>
       </c>
-      <c r="B174" s="15" t="n"/>
-      <c r="C174" s="16" t="n"/>
-      <c r="D174" s="16" t="n"/>
-      <c r="E174" s="14" t="n"/>
-      <c r="F174" s="16" t="n"/>
-      <c r="G174" s="17" t="n"/>
-      <c r="H174" s="17" t="n"/>
-      <c r="I174" s="16" t="n"/>
-      <c r="J174" s="16" t="n"/>
-      <c r="K174" s="16" t="n"/>
-      <c r="L174" s="18">
+      <c r="B174" s="20" t="n"/>
+      <c r="C174" s="8" t="n"/>
+      <c r="D174" s="8" t="n"/>
+      <c r="E174" s="19" t="n"/>
+      <c r="F174" s="8" t="n"/>
+      <c r="G174" s="21" t="n"/>
+      <c r="H174" s="21" t="n"/>
+      <c r="I174" s="8" t="n"/>
+      <c r="J174" s="8" t="n"/>
+      <c r="K174" s="8" t="n"/>
+      <c r="L174" s="22">
         <f>IF(AND(ISNUMBER(G174),ISNUMBER(H174)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G174&amp;","&amp;H174,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="14" t="n">
+      <c r="A175" s="19" t="n">
         <v>173</v>
       </c>
-      <c r="B175" s="15" t="n"/>
-      <c r="C175" s="16" t="n"/>
-      <c r="D175" s="16" t="n"/>
-      <c r="E175" s="14" t="n"/>
-      <c r="F175" s="16" t="n"/>
-      <c r="G175" s="17" t="n"/>
-      <c r="H175" s="17" t="n"/>
-      <c r="I175" s="16" t="n"/>
-      <c r="J175" s="16" t="n"/>
-      <c r="K175" s="16" t="n"/>
-      <c r="L175" s="18">
+      <c r="B175" s="20" t="n"/>
+      <c r="C175" s="8" t="n"/>
+      <c r="D175" s="8" t="n"/>
+      <c r="E175" s="19" t="n"/>
+      <c r="F175" s="8" t="n"/>
+      <c r="G175" s="21" t="n"/>
+      <c r="H175" s="21" t="n"/>
+      <c r="I175" s="8" t="n"/>
+      <c r="J175" s="8" t="n"/>
+      <c r="K175" s="8" t="n"/>
+      <c r="L175" s="22">
         <f>IF(AND(ISNUMBER(G175),ISNUMBER(H175)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G175&amp;","&amp;H175,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="14" t="n">
+      <c r="A176" s="19" t="n">
         <v>174</v>
       </c>
-      <c r="B176" s="15" t="n"/>
-      <c r="C176" s="16" t="n"/>
-      <c r="D176" s="16" t="n"/>
-      <c r="E176" s="14" t="n"/>
-      <c r="F176" s="16" t="n"/>
-      <c r="G176" s="17" t="n"/>
-      <c r="H176" s="17" t="n"/>
-      <c r="I176" s="16" t="n"/>
-      <c r="J176" s="16" t="n"/>
-      <c r="K176" s="16" t="n"/>
-      <c r="L176" s="18">
+      <c r="B176" s="20" t="n"/>
+      <c r="C176" s="8" t="n"/>
+      <c r="D176" s="8" t="n"/>
+      <c r="E176" s="19" t="n"/>
+      <c r="F176" s="8" t="n"/>
+      <c r="G176" s="21" t="n"/>
+      <c r="H176" s="21" t="n"/>
+      <c r="I176" s="8" t="n"/>
+      <c r="J176" s="8" t="n"/>
+      <c r="K176" s="8" t="n"/>
+      <c r="L176" s="22">
         <f>IF(AND(ISNUMBER(G176),ISNUMBER(H176)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G176&amp;","&amp;H176,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="14" t="n">
+      <c r="A177" s="19" t="n">
         <v>175</v>
       </c>
-      <c r="B177" s="15" t="n"/>
-      <c r="C177" s="16" t="n"/>
-      <c r="D177" s="16" t="n"/>
-      <c r="E177" s="14" t="n"/>
-      <c r="F177" s="16" t="n"/>
-      <c r="G177" s="17" t="n"/>
-      <c r="H177" s="17" t="n"/>
-      <c r="I177" s="16" t="n"/>
-      <c r="J177" s="16" t="n"/>
-      <c r="K177" s="16" t="n"/>
-      <c r="L177" s="18">
+      <c r="B177" s="20" t="n"/>
+      <c r="C177" s="8" t="n"/>
+      <c r="D177" s="8" t="n"/>
+      <c r="E177" s="19" t="n"/>
+      <c r="F177" s="8" t="n"/>
+      <c r="G177" s="21" t="n"/>
+      <c r="H177" s="21" t="n"/>
+      <c r="I177" s="8" t="n"/>
+      <c r="J177" s="8" t="n"/>
+      <c r="K177" s="8" t="n"/>
+      <c r="L177" s="22">
         <f>IF(AND(ISNUMBER(G177),ISNUMBER(H177)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G177&amp;","&amp;H177,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="14" t="n">
+      <c r="A178" s="19" t="n">
         <v>176</v>
       </c>
-      <c r="B178" s="15" t="n"/>
-      <c r="C178" s="16" t="n"/>
-      <c r="D178" s="16" t="n"/>
-      <c r="E178" s="14" t="n"/>
-      <c r="F178" s="16" t="n"/>
-      <c r="G178" s="17" t="n"/>
-      <c r="H178" s="17" t="n"/>
-      <c r="I178" s="16" t="n"/>
-      <c r="J178" s="16" t="n"/>
-      <c r="K178" s="16" t="n"/>
-      <c r="L178" s="18">
+      <c r="B178" s="20" t="n"/>
+      <c r="C178" s="8" t="n"/>
+      <c r="D178" s="8" t="n"/>
+      <c r="E178" s="19" t="n"/>
+      <c r="F178" s="8" t="n"/>
+      <c r="G178" s="21" t="n"/>
+      <c r="H178" s="21" t="n"/>
+      <c r="I178" s="8" t="n"/>
+      <c r="J178" s="8" t="n"/>
+      <c r="K178" s="8" t="n"/>
+      <c r="L178" s="22">
         <f>IF(AND(ISNUMBER(G178),ISNUMBER(H178)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G178&amp;","&amp;H178,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="14" t="n">
+      <c r="A179" s="19" t="n">
         <v>177</v>
       </c>
-      <c r="B179" s="15" t="n"/>
-      <c r="C179" s="16" t="n"/>
-      <c r="D179" s="16" t="n"/>
-      <c r="E179" s="14" t="n"/>
-      <c r="F179" s="16" t="n"/>
-      <c r="G179" s="17" t="n"/>
-      <c r="H179" s="17" t="n"/>
-      <c r="I179" s="16" t="n"/>
-      <c r="J179" s="16" t="n"/>
-      <c r="K179" s="16" t="n"/>
-      <c r="L179" s="18">
+      <c r="B179" s="20" t="n"/>
+      <c r="C179" s="8" t="n"/>
+      <c r="D179" s="8" t="n"/>
+      <c r="E179" s="19" t="n"/>
+      <c r="F179" s="8" t="n"/>
+      <c r="G179" s="21" t="n"/>
+      <c r="H179" s="21" t="n"/>
+      <c r="I179" s="8" t="n"/>
+      <c r="J179" s="8" t="n"/>
+      <c r="K179" s="8" t="n"/>
+      <c r="L179" s="22">
         <f>IF(AND(ISNUMBER(G179),ISNUMBER(H179)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G179&amp;","&amp;H179,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="14" t="n">
+      <c r="A180" s="19" t="n">
         <v>178</v>
       </c>
-      <c r="B180" s="15" t="n"/>
-      <c r="C180" s="16" t="n"/>
-      <c r="D180" s="16" t="n"/>
-      <c r="E180" s="14" t="n"/>
-      <c r="F180" s="16" t="n"/>
-      <c r="G180" s="17" t="n"/>
-      <c r="H180" s="17" t="n"/>
-      <c r="I180" s="16" t="n"/>
-      <c r="J180" s="16" t="n"/>
-      <c r="K180" s="16" t="n"/>
-      <c r="L180" s="18">
+      <c r="B180" s="20" t="n"/>
+      <c r="C180" s="8" t="n"/>
+      <c r="D180" s="8" t="n"/>
+      <c r="E180" s="19" t="n"/>
+      <c r="F180" s="8" t="n"/>
+      <c r="G180" s="21" t="n"/>
+      <c r="H180" s="21" t="n"/>
+      <c r="I180" s="8" t="n"/>
+      <c r="J180" s="8" t="n"/>
+      <c r="K180" s="8" t="n"/>
+      <c r="L180" s="22">
         <f>IF(AND(ISNUMBER(G180),ISNUMBER(H180)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G180&amp;","&amp;H180,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="14" t="n">
+      <c r="A181" s="19" t="n">
         <v>179</v>
       </c>
-      <c r="B181" s="15" t="n"/>
-      <c r="C181" s="16" t="n"/>
-      <c r="D181" s="16" t="n"/>
-      <c r="E181" s="14" t="n"/>
-      <c r="F181" s="16" t="n"/>
-      <c r="G181" s="17" t="n"/>
-      <c r="H181" s="17" t="n"/>
-      <c r="I181" s="16" t="n"/>
-      <c r="J181" s="16" t="n"/>
-      <c r="K181" s="16" t="n"/>
-      <c r="L181" s="18">
+      <c r="B181" s="20" t="n"/>
+      <c r="C181" s="8" t="n"/>
+      <c r="D181" s="8" t="n"/>
+      <c r="E181" s="19" t="n"/>
+      <c r="F181" s="8" t="n"/>
+      <c r="G181" s="21" t="n"/>
+      <c r="H181" s="21" t="n"/>
+      <c r="I181" s="8" t="n"/>
+      <c r="J181" s="8" t="n"/>
+      <c r="K181" s="8" t="n"/>
+      <c r="L181" s="22">
         <f>IF(AND(ISNUMBER(G181),ISNUMBER(H181)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G181&amp;","&amp;H181,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="14" t="n">
+      <c r="A182" s="19" t="n">
         <v>180</v>
       </c>
-      <c r="B182" s="15" t="n"/>
-      <c r="C182" s="16" t="n"/>
-      <c r="D182" s="16" t="n"/>
-      <c r="E182" s="14" t="n"/>
-      <c r="F182" s="16" t="n"/>
-      <c r="G182" s="17" t="n"/>
-      <c r="H182" s="17" t="n"/>
-      <c r="I182" s="16" t="n"/>
-      <c r="J182" s="16" t="n"/>
-      <c r="K182" s="16" t="n"/>
-      <c r="L182" s="18">
+      <c r="B182" s="20" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="8" t="n"/>
+      <c r="E182" s="19" t="n"/>
+      <c r="F182" s="8" t="n"/>
+      <c r="G182" s="21" t="n"/>
+      <c r="H182" s="21" t="n"/>
+      <c r="I182" s="8" t="n"/>
+      <c r="J182" s="8" t="n"/>
+      <c r="K182" s="8" t="n"/>
+      <c r="L182" s="22">
         <f>IF(AND(ISNUMBER(G182),ISNUMBER(H182)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G182&amp;","&amp;H182,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="14" t="n">
+      <c r="A183" s="19" t="n">
         <v>181</v>
       </c>
-      <c r="B183" s="15" t="n"/>
-      <c r="C183" s="16" t="n"/>
-      <c r="D183" s="16" t="n"/>
-      <c r="E183" s="14" t="n"/>
-      <c r="F183" s="16" t="n"/>
-      <c r="G183" s="17" t="n"/>
-      <c r="H183" s="17" t="n"/>
-      <c r="I183" s="16" t="n"/>
-      <c r="J183" s="16" t="n"/>
-      <c r="K183" s="16" t="n"/>
-      <c r="L183" s="18">
+      <c r="B183" s="20" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
+      <c r="E183" s="19" t="n"/>
+      <c r="F183" s="8" t="n"/>
+      <c r="G183" s="21" t="n"/>
+      <c r="H183" s="21" t="n"/>
+      <c r="I183" s="8" t="n"/>
+      <c r="J183" s="8" t="n"/>
+      <c r="K183" s="8" t="n"/>
+      <c r="L183" s="22">
         <f>IF(AND(ISNUMBER(G183),ISNUMBER(H183)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G183&amp;","&amp;H183,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="14" t="n">
+      <c r="A184" s="19" t="n">
         <v>182</v>
       </c>
-      <c r="B184" s="15" t="n"/>
-      <c r="C184" s="16" t="n"/>
-      <c r="D184" s="16" t="n"/>
-      <c r="E184" s="14" t="n"/>
-      <c r="F184" s="16" t="n"/>
-      <c r="G184" s="17" t="n"/>
-      <c r="H184" s="17" t="n"/>
-      <c r="I184" s="16" t="n"/>
-      <c r="J184" s="16" t="n"/>
-      <c r="K184" s="16" t="n"/>
-      <c r="L184" s="18">
+      <c r="B184" s="20" t="n"/>
+      <c r="C184" s="8" t="n"/>
+      <c r="D184" s="8" t="n"/>
+      <c r="E184" s="19" t="n"/>
+      <c r="F184" s="8" t="n"/>
+      <c r="G184" s="21" t="n"/>
+      <c r="H184" s="21" t="n"/>
+      <c r="I184" s="8" t="n"/>
+      <c r="J184" s="8" t="n"/>
+      <c r="K184" s="8" t="n"/>
+      <c r="L184" s="22">
         <f>IF(AND(ISNUMBER(G184),ISNUMBER(H184)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G184&amp;","&amp;H184,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="14" t="n">
+      <c r="A185" s="19" t="n">
         <v>183</v>
       </c>
-      <c r="B185" s="15" t="n"/>
-      <c r="C185" s="16" t="n"/>
-      <c r="D185" s="16" t="n"/>
-      <c r="E185" s="14" t="n"/>
-      <c r="F185" s="16" t="n"/>
-      <c r="G185" s="17" t="n"/>
-      <c r="H185" s="17" t="n"/>
-      <c r="I185" s="16" t="n"/>
-      <c r="J185" s="16" t="n"/>
-      <c r="K185" s="16" t="n"/>
-      <c r="L185" s="18">
+      <c r="B185" s="20" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="19" t="n"/>
+      <c r="F185" s="8" t="n"/>
+      <c r="G185" s="21" t="n"/>
+      <c r="H185" s="21" t="n"/>
+      <c r="I185" s="8" t="n"/>
+      <c r="J185" s="8" t="n"/>
+      <c r="K185" s="8" t="n"/>
+      <c r="L185" s="22">
         <f>IF(AND(ISNUMBER(G185),ISNUMBER(H185)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G185&amp;","&amp;H185,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="14" t="n">
+      <c r="A186" s="19" t="n">
         <v>184</v>
       </c>
-      <c r="B186" s="15" t="n"/>
-      <c r="C186" s="16" t="n"/>
-      <c r="D186" s="16" t="n"/>
-      <c r="E186" s="14" t="n"/>
-      <c r="F186" s="16" t="n"/>
-      <c r="G186" s="17" t="n"/>
-      <c r="H186" s="17" t="n"/>
-      <c r="I186" s="16" t="n"/>
-      <c r="J186" s="16" t="n"/>
-      <c r="K186" s="16" t="n"/>
-      <c r="L186" s="18">
+      <c r="B186" s="20" t="n"/>
+      <c r="C186" s="8" t="n"/>
+      <c r="D186" s="8" t="n"/>
+      <c r="E186" s="19" t="n"/>
+      <c r="F186" s="8" t="n"/>
+      <c r="G186" s="21" t="n"/>
+      <c r="H186" s="21" t="n"/>
+      <c r="I186" s="8" t="n"/>
+      <c r="J186" s="8" t="n"/>
+      <c r="K186" s="8" t="n"/>
+      <c r="L186" s="22">
         <f>IF(AND(ISNUMBER(G186),ISNUMBER(H186)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G186&amp;","&amp;H186,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="14" t="n">
+      <c r="A187" s="19" t="n">
         <v>185</v>
       </c>
-      <c r="B187" s="15" t="n"/>
-      <c r="C187" s="16" t="n"/>
-      <c r="D187" s="16" t="n"/>
-      <c r="E187" s="14" t="n"/>
-      <c r="F187" s="16" t="n"/>
-      <c r="G187" s="17" t="n"/>
-      <c r="H187" s="17" t="n"/>
-      <c r="I187" s="16" t="n"/>
-      <c r="J187" s="16" t="n"/>
-      <c r="K187" s="16" t="n"/>
-      <c r="L187" s="18">
+      <c r="B187" s="20" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="19" t="n"/>
+      <c r="F187" s="8" t="n"/>
+      <c r="G187" s="21" t="n"/>
+      <c r="H187" s="21" t="n"/>
+      <c r="I187" s="8" t="n"/>
+      <c r="J187" s="8" t="n"/>
+      <c r="K187" s="8" t="n"/>
+      <c r="L187" s="22">
         <f>IF(AND(ISNUMBER(G187),ISNUMBER(H187)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G187&amp;","&amp;H187,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="14" t="n">
+      <c r="A188" s="19" t="n">
         <v>186</v>
       </c>
-      <c r="B188" s="15" t="n"/>
-      <c r="C188" s="16" t="n"/>
-      <c r="D188" s="16" t="n"/>
-      <c r="E188" s="14" t="n"/>
-      <c r="F188" s="16" t="n"/>
-      <c r="G188" s="17" t="n"/>
-      <c r="H188" s="17" t="n"/>
-      <c r="I188" s="16" t="n"/>
-      <c r="J188" s="16" t="n"/>
-      <c r="K188" s="16" t="n"/>
-      <c r="L188" s="18">
+      <c r="B188" s="20" t="n"/>
+      <c r="C188" s="8" t="n"/>
+      <c r="D188" s="8" t="n"/>
+      <c r="E188" s="19" t="n"/>
+      <c r="F188" s="8" t="n"/>
+      <c r="G188" s="21" t="n"/>
+      <c r="H188" s="21" t="n"/>
+      <c r="I188" s="8" t="n"/>
+      <c r="J188" s="8" t="n"/>
+      <c r="K188" s="8" t="n"/>
+      <c r="L188" s="22">
         <f>IF(AND(ISNUMBER(G188),ISNUMBER(H188)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G188&amp;","&amp;H188,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="14" t="n">
+      <c r="A189" s="19" t="n">
         <v>187</v>
       </c>
-      <c r="B189" s="15" t="n"/>
-      <c r="C189" s="16" t="n"/>
-      <c r="D189" s="16" t="n"/>
-      <c r="E189" s="14" t="n"/>
-      <c r="F189" s="16" t="n"/>
-      <c r="G189" s="17" t="n"/>
-      <c r="H189" s="17" t="n"/>
-      <c r="I189" s="16" t="n"/>
-      <c r="J189" s="16" t="n"/>
-      <c r="K189" s="16" t="n"/>
-      <c r="L189" s="18">
+      <c r="B189" s="20" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="19" t="n"/>
+      <c r="F189" s="8" t="n"/>
+      <c r="G189" s="21" t="n"/>
+      <c r="H189" s="21" t="n"/>
+      <c r="I189" s="8" t="n"/>
+      <c r="J189" s="8" t="n"/>
+      <c r="K189" s="8" t="n"/>
+      <c r="L189" s="22">
         <f>IF(AND(ISNUMBER(G189),ISNUMBER(H189)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G189&amp;","&amp;H189,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="14" t="n">
+      <c r="A190" s="19" t="n">
         <v>188</v>
       </c>
-      <c r="B190" s="15" t="n"/>
-      <c r="C190" s="16" t="n"/>
-      <c r="D190" s="16" t="n"/>
-      <c r="E190" s="14" t="n"/>
-      <c r="F190" s="16" t="n"/>
-      <c r="G190" s="17" t="n"/>
-      <c r="H190" s="17" t="n"/>
-      <c r="I190" s="16" t="n"/>
-      <c r="J190" s="16" t="n"/>
-      <c r="K190" s="16" t="n"/>
-      <c r="L190" s="18">
+      <c r="B190" s="20" t="n"/>
+      <c r="C190" s="8" t="n"/>
+      <c r="D190" s="8" t="n"/>
+      <c r="E190" s="19" t="n"/>
+      <c r="F190" s="8" t="n"/>
+      <c r="G190" s="21" t="n"/>
+      <c r="H190" s="21" t="n"/>
+      <c r="I190" s="8" t="n"/>
+      <c r="J190" s="8" t="n"/>
+      <c r="K190" s="8" t="n"/>
+      <c r="L190" s="22">
         <f>IF(AND(ISNUMBER(G190),ISNUMBER(H190)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G190&amp;","&amp;H190,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="14" t="n">
+      <c r="A191" s="19" t="n">
         <v>189</v>
       </c>
-      <c r="B191" s="15" t="n"/>
-      <c r="C191" s="16" t="n"/>
-      <c r="D191" s="16" t="n"/>
-      <c r="E191" s="14" t="n"/>
-      <c r="F191" s="16" t="n"/>
-      <c r="G191" s="17" t="n"/>
-      <c r="H191" s="17" t="n"/>
-      <c r="I191" s="16" t="n"/>
-      <c r="J191" s="16" t="n"/>
-      <c r="K191" s="16" t="n"/>
-      <c r="L191" s="18">
+      <c r="B191" s="20" t="n"/>
+      <c r="C191" s="8" t="n"/>
+      <c r="D191" s="8" t="n"/>
+      <c r="E191" s="19" t="n"/>
+      <c r="F191" s="8" t="n"/>
+      <c r="G191" s="21" t="n"/>
+      <c r="H191" s="21" t="n"/>
+      <c r="I191" s="8" t="n"/>
+      <c r="J191" s="8" t="n"/>
+      <c r="K191" s="8" t="n"/>
+      <c r="L191" s="22">
         <f>IF(AND(ISNUMBER(G191),ISNUMBER(H191)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G191&amp;","&amp;H191,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="14" t="n">
+      <c r="A192" s="19" t="n">
         <v>190</v>
       </c>
-      <c r="B192" s="15" t="n"/>
-      <c r="C192" s="16" t="n"/>
-      <c r="D192" s="16" t="n"/>
-      <c r="E192" s="14" t="n"/>
-      <c r="F192" s="16" t="n"/>
-      <c r="G192" s="17" t="n"/>
-      <c r="H192" s="17" t="n"/>
-      <c r="I192" s="16" t="n"/>
-      <c r="J192" s="16" t="n"/>
-      <c r="K192" s="16" t="n"/>
-      <c r="L192" s="18">
+      <c r="B192" s="20" t="n"/>
+      <c r="C192" s="8" t="n"/>
+      <c r="D192" s="8" t="n"/>
+      <c r="E192" s="19" t="n"/>
+      <c r="F192" s="8" t="n"/>
+      <c r="G192" s="21" t="n"/>
+      <c r="H192" s="21" t="n"/>
+      <c r="I192" s="8" t="n"/>
+      <c r="J192" s="8" t="n"/>
+      <c r="K192" s="8" t="n"/>
+      <c r="L192" s="22">
         <f>IF(AND(ISNUMBER(G192),ISNUMBER(H192)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G192&amp;","&amp;H192,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="14" t="n">
+      <c r="A193" s="19" t="n">
         <v>191</v>
       </c>
-      <c r="B193" s="15" t="n"/>
-      <c r="C193" s="16" t="n"/>
-      <c r="D193" s="16" t="n"/>
-      <c r="E193" s="14" t="n"/>
-      <c r="F193" s="16" t="n"/>
-      <c r="G193" s="17" t="n"/>
-      <c r="H193" s="17" t="n"/>
-      <c r="I193" s="16" t="n"/>
-      <c r="J193" s="16" t="n"/>
-      <c r="K193" s="16" t="n"/>
-      <c r="L193" s="18">
+      <c r="B193" s="20" t="n"/>
+      <c r="C193" s="8" t="n"/>
+      <c r="D193" s="8" t="n"/>
+      <c r="E193" s="19" t="n"/>
+      <c r="F193" s="8" t="n"/>
+      <c r="G193" s="21" t="n"/>
+      <c r="H193" s="21" t="n"/>
+      <c r="I193" s="8" t="n"/>
+      <c r="J193" s="8" t="n"/>
+      <c r="K193" s="8" t="n"/>
+      <c r="L193" s="22">
         <f>IF(AND(ISNUMBER(G193),ISNUMBER(H193)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G193&amp;","&amp;H193,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="14" t="n">
+      <c r="A194" s="19" t="n">
         <v>192</v>
       </c>
-      <c r="B194" s="15" t="n"/>
-      <c r="C194" s="16" t="n"/>
-      <c r="D194" s="16" t="n"/>
-      <c r="E194" s="14" t="n"/>
-      <c r="F194" s="16" t="n"/>
-      <c r="G194" s="17" t="n"/>
-      <c r="H194" s="17" t="n"/>
-      <c r="I194" s="16" t="n"/>
-      <c r="J194" s="16" t="n"/>
-      <c r="K194" s="16" t="n"/>
-      <c r="L194" s="18">
+      <c r="B194" s="20" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="19" t="n"/>
+      <c r="F194" s="8" t="n"/>
+      <c r="G194" s="21" t="n"/>
+      <c r="H194" s="21" t="n"/>
+      <c r="I194" s="8" t="n"/>
+      <c r="J194" s="8" t="n"/>
+      <c r="K194" s="8" t="n"/>
+      <c r="L194" s="22">
         <f>IF(AND(ISNUMBER(G194),ISNUMBER(H194)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G194&amp;","&amp;H194,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="14" t="n">
+      <c r="A195" s="19" t="n">
         <v>193</v>
       </c>
-      <c r="B195" s="15" t="n"/>
-      <c r="C195" s="16" t="n"/>
-      <c r="D195" s="16" t="n"/>
-      <c r="E195" s="14" t="n"/>
-      <c r="F195" s="16" t="n"/>
-      <c r="G195" s="17" t="n"/>
-      <c r="H195" s="17" t="n"/>
-      <c r="I195" s="16" t="n"/>
-      <c r="J195" s="16" t="n"/>
-      <c r="K195" s="16" t="n"/>
-      <c r="L195" s="18">
+      <c r="B195" s="20" t="n"/>
+      <c r="C195" s="8" t="n"/>
+      <c r="D195" s="8" t="n"/>
+      <c r="E195" s="19" t="n"/>
+      <c r="F195" s="8" t="n"/>
+      <c r="G195" s="21" t="n"/>
+      <c r="H195" s="21" t="n"/>
+      <c r="I195" s="8" t="n"/>
+      <c r="J195" s="8" t="n"/>
+      <c r="K195" s="8" t="n"/>
+      <c r="L195" s="22">
         <f>IF(AND(ISNUMBER(G195),ISNUMBER(H195)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G195&amp;","&amp;H195,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="14" t="n">
+      <c r="A196" s="19" t="n">
         <v>194</v>
       </c>
-      <c r="B196" s="15" t="n"/>
-      <c r="C196" s="16" t="n"/>
-      <c r="D196" s="16" t="n"/>
-      <c r="E196" s="14" t="n"/>
-      <c r="F196" s="16" t="n"/>
-      <c r="G196" s="17" t="n"/>
-      <c r="H196" s="17" t="n"/>
-      <c r="I196" s="16" t="n"/>
-      <c r="J196" s="16" t="n"/>
-      <c r="K196" s="16" t="n"/>
-      <c r="L196" s="18">
+      <c r="B196" s="20" t="n"/>
+      <c r="C196" s="8" t="n"/>
+      <c r="D196" s="8" t="n"/>
+      <c r="E196" s="19" t="n"/>
+      <c r="F196" s="8" t="n"/>
+      <c r="G196" s="21" t="n"/>
+      <c r="H196" s="21" t="n"/>
+      <c r="I196" s="8" t="n"/>
+      <c r="J196" s="8" t="n"/>
+      <c r="K196" s="8" t="n"/>
+      <c r="L196" s="22">
         <f>IF(AND(ISNUMBER(G196),ISNUMBER(H196)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G196&amp;","&amp;H196,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="14" t="n">
+      <c r="A197" s="19" t="n">
         <v>195</v>
       </c>
-      <c r="B197" s="15" t="n"/>
-      <c r="C197" s="16" t="n"/>
-      <c r="D197" s="16" t="n"/>
-      <c r="E197" s="14" t="n"/>
-      <c r="F197" s="16" t="n"/>
-      <c r="G197" s="17" t="n"/>
-      <c r="H197" s="17" t="n"/>
-      <c r="I197" s="16" t="n"/>
-      <c r="J197" s="16" t="n"/>
-      <c r="K197" s="16" t="n"/>
-      <c r="L197" s="18">
+      <c r="B197" s="20" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
+      <c r="E197" s="19" t="n"/>
+      <c r="F197" s="8" t="n"/>
+      <c r="G197" s="21" t="n"/>
+      <c r="H197" s="21" t="n"/>
+      <c r="I197" s="8" t="n"/>
+      <c r="J197" s="8" t="n"/>
+      <c r="K197" s="8" t="n"/>
+      <c r="L197" s="22">
         <f>IF(AND(ISNUMBER(G197),ISNUMBER(H197)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G197&amp;","&amp;H197,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="14" t="n">
+      <c r="A198" s="19" t="n">
         <v>196</v>
       </c>
-      <c r="B198" s="15" t="n"/>
-      <c r="C198" s="16" t="n"/>
-      <c r="D198" s="16" t="n"/>
-      <c r="E198" s="14" t="n"/>
-      <c r="F198" s="16" t="n"/>
-      <c r="G198" s="17" t="n"/>
-      <c r="H198" s="17" t="n"/>
-      <c r="I198" s="16" t="n"/>
-      <c r="J198" s="16" t="n"/>
-      <c r="K198" s="16" t="n"/>
-      <c r="L198" s="18">
+      <c r="B198" s="20" t="n"/>
+      <c r="C198" s="8" t="n"/>
+      <c r="D198" s="8" t="n"/>
+      <c r="E198" s="19" t="n"/>
+      <c r="F198" s="8" t="n"/>
+      <c r="G198" s="21" t="n"/>
+      <c r="H198" s="21" t="n"/>
+      <c r="I198" s="8" t="n"/>
+      <c r="J198" s="8" t="n"/>
+      <c r="K198" s="8" t="n"/>
+      <c r="L198" s="22">
         <f>IF(AND(ISNUMBER(G198),ISNUMBER(H198)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G198&amp;","&amp;H198,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="14" t="n">
+      <c r="A199" s="19" t="n">
         <v>197</v>
       </c>
-      <c r="B199" s="15" t="n"/>
-      <c r="C199" s="16" t="n"/>
-      <c r="D199" s="16" t="n"/>
-      <c r="E199" s="14" t="n"/>
-      <c r="F199" s="16" t="n"/>
-      <c r="G199" s="17" t="n"/>
-      <c r="H199" s="17" t="n"/>
-      <c r="I199" s="16" t="n"/>
-      <c r="J199" s="16" t="n"/>
-      <c r="K199" s="16" t="n"/>
-      <c r="L199" s="18">
+      <c r="B199" s="20" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="19" t="n"/>
+      <c r="F199" s="8" t="n"/>
+      <c r="G199" s="21" t="n"/>
+      <c r="H199" s="21" t="n"/>
+      <c r="I199" s="8" t="n"/>
+      <c r="J199" s="8" t="n"/>
+      <c r="K199" s="8" t="n"/>
+      <c r="L199" s="22">
         <f>IF(AND(ISNUMBER(G199),ISNUMBER(H199)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G199&amp;","&amp;H199,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="14" t="n">
+      <c r="A200" s="19" t="n">
         <v>198</v>
       </c>
-      <c r="B200" s="15" t="n"/>
-      <c r="C200" s="16" t="n"/>
-      <c r="D200" s="16" t="n"/>
-      <c r="E200" s="14" t="n"/>
-      <c r="F200" s="16" t="n"/>
-      <c r="G200" s="17" t="n"/>
-      <c r="H200" s="17" t="n"/>
-      <c r="I200" s="16" t="n"/>
-      <c r="J200" s="16" t="n"/>
-      <c r="K200" s="16" t="n"/>
-      <c r="L200" s="18">
+      <c r="B200" s="20" t="n"/>
+      <c r="C200" s="8" t="n"/>
+      <c r="D200" s="8" t="n"/>
+      <c r="E200" s="19" t="n"/>
+      <c r="F200" s="8" t="n"/>
+      <c r="G200" s="21" t="n"/>
+      <c r="H200" s="21" t="n"/>
+      <c r="I200" s="8" t="n"/>
+      <c r="J200" s="8" t="n"/>
+      <c r="K200" s="8" t="n"/>
+      <c r="L200" s="22">
         <f>IF(AND(ISNUMBER(G200),ISNUMBER(H200)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G200&amp;","&amp;H200,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="14" t="n">
+      <c r="A201" s="19" t="n">
         <v>199</v>
       </c>
-      <c r="B201" s="15" t="n"/>
-      <c r="C201" s="16" t="n"/>
-      <c r="D201" s="16" t="n"/>
-      <c r="E201" s="14" t="n"/>
-      <c r="F201" s="16" t="n"/>
-      <c r="G201" s="17" t="n"/>
-      <c r="H201" s="17" t="n"/>
-      <c r="I201" s="16" t="n"/>
-      <c r="J201" s="16" t="n"/>
-      <c r="K201" s="16" t="n"/>
-      <c r="L201" s="18">
+      <c r="B201" s="20" t="n"/>
+      <c r="C201" s="8" t="n"/>
+      <c r="D201" s="8" t="n"/>
+      <c r="E201" s="19" t="n"/>
+      <c r="F201" s="8" t="n"/>
+      <c r="G201" s="21" t="n"/>
+      <c r="H201" s="21" t="n"/>
+      <c r="I201" s="8" t="n"/>
+      <c r="J201" s="8" t="n"/>
+      <c r="K201" s="8" t="n"/>
+      <c r="L201" s="22">
         <f>IF(AND(ISNUMBER(G201),ISNUMBER(H201)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G201&amp;","&amp;H201,"Voir sur la carte"),"")</f>
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="14" t="n">
+      <c r="A202" s="19" t="n">
         <v>200</v>
       </c>
-      <c r="B202" s="15" t="n"/>
-      <c r="C202" s="16" t="n"/>
-      <c r="D202" s="16" t="n"/>
-      <c r="E202" s="14" t="n"/>
-      <c r="F202" s="16" t="n"/>
-      <c r="G202" s="17" t="n"/>
-      <c r="H202" s="17" t="n"/>
-      <c r="I202" s="16" t="n"/>
-      <c r="J202" s="16" t="n"/>
-      <c r="K202" s="16" t="n"/>
-      <c r="L202" s="18">
+      <c r="B202" s="20" t="n"/>
+      <c r="C202" s="8" t="n"/>
+      <c r="D202" s="8" t="n"/>
+      <c r="E202" s="19" t="n"/>
+      <c r="F202" s="8" t="n"/>
+      <c r="G202" s="21" t="n"/>
+      <c r="H202" s="21" t="n"/>
+      <c r="I202" s="8" t="n"/>
+      <c r="J202" s="8" t="n"/>
+      <c r="K202" s="8" t="n"/>
+      <c r="L202" s="22">
         <f>IF(AND(ISNUMBER(G202),ISNUMBER(H202)),HYPERLINK("https://www.google.com/maps/search/?api=1&amp;query="&amp;G202&amp;","&amp;H202,"Voir sur la carte"),"")</f>
         <v/>
       </c>
@@ -5445,7 +5701,7 @@
   </sheetData>
   <autoFilter ref="A1:L202"/>
   <dataValidations count="3">
-    <dataValidation sqref="E3:E202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Type du point" prompt="Lequel choisir : voir la feuille « Types »" type="list">
       <formula1>"Monument,Site archéologique,Musée,Édifice religieux,Palais / forteresse,Site naturel,Ville / village,Autre"</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Latitude" error="Latitude attendue entre 18 et 38 (Algérie), avec un point décimal" type="decimal" operator="between">
@@ -5461,7 +5717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
